--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR20"/>
+  <dimension ref="A1:AS20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,6 +644,11 @@
           <t>2026-04-07</t>
         </is>
       </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -778,6 +783,9 @@
         <v>4420</v>
       </c>
       <c r="AR2" t="n">
+        <v>4442</v>
+      </c>
+      <c r="AS2" t="n">
         <v>4442</v>
       </c>
     </row>
@@ -886,6 +894,9 @@
       <c r="AR3" t="n">
         <v>559</v>
       </c>
+      <c r="AS3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1022,6 +1033,9 @@
       <c r="AR4" t="n">
         <v>1788</v>
       </c>
+      <c r="AS4" t="n">
+        <v>1788</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1156,7 +1170,10 @@
         <v>658</v>
       </c>
       <c r="AR5" t="n">
-        <v>694</v>
+        <v>690</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>695</v>
       </c>
     </row>
     <row r="6">
@@ -1264,6 +1281,9 @@
       <c r="AR6" t="n">
         <v>2</v>
       </c>
+      <c r="AS6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1398,6 +1418,9 @@
         <v>81</v>
       </c>
       <c r="AR7" t="n">
+        <v>49</v>
+      </c>
+      <c r="AS7" t="n">
         <v>48</v>
       </c>
     </row>
@@ -1506,6 +1529,9 @@
       <c r="AR8" t="n">
         <v>19</v>
       </c>
+      <c r="AS8" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1612,6 +1638,9 @@
       <c r="AR9" t="n">
         <v>2</v>
       </c>
+      <c r="AS9" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1748,6 +1777,9 @@
       <c r="AR10" t="n">
         <v>1272</v>
       </c>
+      <c r="AS10" t="n">
+        <v>1272</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1882,7 +1914,10 @@
         <v>62</v>
       </c>
       <c r="AR11" t="n">
-        <v>58</v>
+        <v>61</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>57</v>
       </c>
     </row>
     <row r="12">
@@ -2020,6 +2055,9 @@
       <c r="AR12" t="n">
         <v>1</v>
       </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -2153,7 +2191,10 @@
       <c r="AQ13" t="n">
         <v>1</v>
       </c>
-      <c r="AR13" t="inlineStr"/>
+      <c r="AR13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -2287,7 +2328,10 @@
       <c r="AQ14" t="n">
         <v>79</v>
       </c>
-      <c r="AR14" t="inlineStr"/>
+      <c r="AR14" t="n">
+        <v>47</v>
+      </c>
+      <c r="AS14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -2424,6 +2468,9 @@
       <c r="AR15" t="n">
         <v>64</v>
       </c>
+      <c r="AS15" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -2560,6 +2607,9 @@
       <c r="AR16" t="n">
         <v>864</v>
       </c>
+      <c r="AS16" t="n">
+        <v>864</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -2694,6 +2744,9 @@
         <v>1524</v>
       </c>
       <c r="AR17" t="n">
+        <v>1524</v>
+      </c>
+      <c r="AS17" t="n">
         <v>1536</v>
       </c>
     </row>
@@ -2830,7 +2883,10 @@
         <v>6.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>6.37</v>
+        <v>6.372093023255814</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>6.23</v>
       </c>
     </row>
     <row r="19">
@@ -2966,7 +3022,10 @@
         <v>133.0769230769231</v>
       </c>
       <c r="AR19" t="n">
-        <v>135.59</v>
+        <v>135.5912408759124</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>138.74</v>
       </c>
     </row>
     <row r="20">
@@ -3187,7 +3246,12 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -1778,7 +1778,7 @@
         <v>1272</v>
       </c>
       <c r="AS10" t="n">
-        <v>1272</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="11">
@@ -1917,7 +1917,7 @@
         <v>61</v>
       </c>
       <c r="AS11" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12">
@@ -2056,7 +2056,7 @@
         <v>1</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -2608,7 +2608,7 @@
         <v>864</v>
       </c>
       <c r="AS16" t="n">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="17">
@@ -2886,7 +2886,7 @@
         <v>6.372093023255814</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.23</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="19">
@@ -3025,7 +3025,7 @@
         <v>135.5912408759124</v>
       </c>
       <c r="AS19" t="n">
-        <v>138.74</v>
+        <v>138.08</v>
       </c>
     </row>
     <row r="20">

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS20"/>
+  <dimension ref="A1:AT20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -649,6 +649,11 @@
           <t>2026-04-08</t>
         </is>
       </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -787,6 +792,9 @@
       </c>
       <c r="AS2" t="n">
         <v>4442</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4441</v>
       </c>
     </row>
     <row r="3">
@@ -897,6 +905,9 @@
       <c r="AS3" t="n">
         <v>559</v>
       </c>
+      <c r="AT3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1036,6 +1047,9 @@
       <c r="AS4" t="n">
         <v>1788</v>
       </c>
+      <c r="AT4" t="n">
+        <v>1788</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1174,6 +1188,9 @@
       </c>
       <c r="AS5" t="n">
         <v>695</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>694</v>
       </c>
     </row>
     <row r="6">
@@ -1284,6 +1301,9 @@
       <c r="AS6" t="n">
         <v>2</v>
       </c>
+      <c r="AT6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1421,6 +1441,9 @@
         <v>49</v>
       </c>
       <c r="AS7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT7" t="n">
         <v>48</v>
       </c>
     </row>
@@ -1532,6 +1555,9 @@
       <c r="AS8" t="n">
         <v>19</v>
       </c>
+      <c r="AT8" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1641,6 +1667,9 @@
       <c r="AS9" t="n">
         <v>2</v>
       </c>
+      <c r="AT9" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1780,6 +1809,9 @@
       <c r="AS10" t="n">
         <v>1273</v>
       </c>
+      <c r="AT10" t="n">
+        <v>1276</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1919,6 +1951,9 @@
       <c r="AS11" t="n">
         <v>56</v>
       </c>
+      <c r="AT11" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -2058,6 +2093,9 @@
       <c r="AS12" t="n">
         <v>1</v>
       </c>
+      <c r="AT12" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -2195,6 +2233,7 @@
         <v>1</v>
       </c>
       <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -2332,6 +2371,7 @@
         <v>47</v>
       </c>
       <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -2471,6 +2511,9 @@
       <c r="AS15" t="n">
         <v>64</v>
       </c>
+      <c r="AT15" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -2610,6 +2653,9 @@
       <c r="AS16" t="n">
         <v>863</v>
       </c>
+      <c r="AT16" t="n">
+        <v>859</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -2749,6 +2795,9 @@
       <c r="AS17" t="n">
         <v>1536</v>
       </c>
+      <c r="AT17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -2888,6 +2937,9 @@
       <c r="AS18" t="n">
         <v>6.25</v>
       </c>
+      <c r="AT18" t="n">
+        <v>6.18</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -3027,6 +3079,9 @@
       <c r="AS19" t="n">
         <v>138.08</v>
       </c>
+      <c r="AT19" t="n">
+        <v>139.05</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -3252,6 +3307,11 @@
       <c r="AS20" t="inlineStr">
         <is>
           <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -1190,7 +1190,7 @@
         <v>695</v>
       </c>
       <c r="AT5" t="n">
-        <v>694</v>
+        <v>690</v>
       </c>
     </row>
     <row r="6">
@@ -1952,7 +1952,7 @@
         <v>56</v>
       </c>
       <c r="AT11" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12">

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -1190,7 +1190,7 @@
         <v>695</v>
       </c>
       <c r="AT5" t="n">
-        <v>690</v>
+        <v>698</v>
       </c>
     </row>
     <row r="6">
@@ -1444,7 +1444,7 @@
         <v>48</v>
       </c>
       <c r="AT7" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -1810,7 +1810,7 @@
         <v>1273</v>
       </c>
       <c r="AT10" t="n">
-        <v>1276</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="11">
@@ -1952,7 +1952,7 @@
         <v>56</v>
       </c>
       <c r="AT11" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
@@ -2094,7 +2094,7 @@
         <v>1</v>
       </c>
       <c r="AT12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -2654,7 +2654,7 @@
         <v>863</v>
       </c>
       <c r="AT16" t="n">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="17">
@@ -2938,7 +2938,7 @@
         <v>6.25</v>
       </c>
       <c r="AT18" t="n">
-        <v>6.18</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="19">
@@ -3080,7 +3080,7 @@
         <v>138.08</v>
       </c>
       <c r="AT19" t="n">
-        <v>139.05</v>
+        <v>138.39</v>
       </c>
     </row>
     <row r="20">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -1190,7 +1190,7 @@
         <v>695</v>
       </c>
       <c r="AT5" t="n">
-        <v>698</v>
+        <v>732</v>
       </c>
     </row>
     <row r="6">
@@ -1444,7 +1444,7 @@
         <v>48</v>
       </c>
       <c r="AT7" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1810,7 +1810,7 @@
         <v>1273</v>
       </c>
       <c r="AT10" t="n">
-        <v>1277</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="11">
@@ -1952,7 +1952,7 @@
         <v>56</v>
       </c>
       <c r="AT11" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12">
@@ -2094,7 +2094,7 @@
         <v>1</v>
       </c>
       <c r="AT12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -2654,7 +2654,7 @@
         <v>863</v>
       </c>
       <c r="AT16" t="n">
-        <v>858</v>
+        <v>855</v>
       </c>
     </row>
     <row r="17">
@@ -2938,7 +2938,7 @@
         <v>6.25</v>
       </c>
       <c r="AT18" t="n">
-        <v>6.2</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="19">
@@ -3080,7 +3080,7 @@
         <v>138.08</v>
       </c>
       <c r="AT19" t="n">
-        <v>138.39</v>
+        <v>136.44</v>
       </c>
     </row>
     <row r="20">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT20"/>
+  <dimension ref="A1:AU20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,6 +654,11 @@
           <t>2026-04-09</t>
         </is>
       </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -794,6 +799,9 @@
         <v>4442</v>
       </c>
       <c r="AT2" t="n">
+        <v>4441</v>
+      </c>
+      <c r="AU2" t="n">
         <v>4441</v>
       </c>
     </row>
@@ -908,6 +916,9 @@
       <c r="AT3" t="n">
         <v>559</v>
       </c>
+      <c r="AU3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1050,6 +1061,9 @@
       <c r="AT4" t="n">
         <v>1788</v>
       </c>
+      <c r="AU4" t="n">
+        <v>1788</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1190,6 +1204,9 @@
         <v>695</v>
       </c>
       <c r="AT5" t="n">
+        <v>732</v>
+      </c>
+      <c r="AU5" t="n">
         <v>732</v>
       </c>
     </row>
@@ -1304,6 +1321,9 @@
       <c r="AT6" t="n">
         <v>2</v>
       </c>
+      <c r="AU6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1444,6 +1464,9 @@
         <v>48</v>
       </c>
       <c r="AT7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1558,6 +1581,9 @@
       <c r="AT8" t="n">
         <v>19</v>
       </c>
+      <c r="AU8" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1670,6 +1696,9 @@
       <c r="AT9" t="n">
         <v>2</v>
       </c>
+      <c r="AU9" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1812,6 +1841,9 @@
       <c r="AT10" t="n">
         <v>1280</v>
       </c>
+      <c r="AU10" t="n">
+        <v>1280</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1954,6 +1986,9 @@
       <c r="AT11" t="n">
         <v>56</v>
       </c>
+      <c r="AU11" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -2096,6 +2131,9 @@
       <c r="AT12" t="n">
         <v>7</v>
       </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -2234,6 +2272,7 @@
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -2372,6 +2411,7 @@
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -2514,6 +2554,9 @@
       <c r="AT15" t="n">
         <v>64</v>
       </c>
+      <c r="AU15" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -2656,6 +2699,9 @@
       <c r="AT16" t="n">
         <v>855</v>
       </c>
+      <c r="AU16" t="n">
+        <v>855</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -2798,6 +2844,9 @@
       <c r="AT17" t="n">
         <v>1536</v>
       </c>
+      <c r="AU17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -2940,6 +2989,9 @@
       <c r="AT18" t="n">
         <v>6.27</v>
       </c>
+      <c r="AU18" t="n">
+        <v>6.13</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -3082,6 +3134,9 @@
       <c r="AT19" t="n">
         <v>136.44</v>
       </c>
+      <c r="AU19" t="n">
+        <v>139.47</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -3312,6 +3367,11 @@
       <c r="AT20" t="inlineStr">
         <is>
           <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -1207,7 +1207,7 @@
         <v>732</v>
       </c>
       <c r="AU5" t="n">
-        <v>732</v>
+        <v>727</v>
       </c>
     </row>
     <row r="6">
@@ -1842,7 +1842,7 @@
         <v>1280</v>
       </c>
       <c r="AU10" t="n">
-        <v>1280</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="11">
@@ -1987,7 +1987,7 @@
         <v>56</v>
       </c>
       <c r="AU11" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
@@ -2132,7 +2132,7 @@
         <v>7</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -2700,7 +2700,7 @@
         <v>855</v>
       </c>
       <c r="AU16" t="n">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="17">
@@ -2990,7 +2990,7 @@
         <v>6.27</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.13</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="19">
@@ -3135,7 +3135,7 @@
         <v>136.44</v>
       </c>
       <c r="AU19" t="n">
-        <v>139.47</v>
+        <v>138.81</v>
       </c>
     </row>
     <row r="20">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -1207,7 +1207,7 @@
         <v>732</v>
       </c>
       <c r="AU5" t="n">
-        <v>727</v>
+        <v>724</v>
       </c>
     </row>
     <row r="6">
@@ -1842,7 +1842,7 @@
         <v>1280</v>
       </c>
       <c r="AU10" t="n">
-        <v>1281</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="11">
@@ -1987,7 +1987,7 @@
         <v>56</v>
       </c>
       <c r="AU11" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12">
@@ -2132,7 +2132,7 @@
         <v>7</v>
       </c>
       <c r="AU12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -2700,7 +2700,7 @@
         <v>855</v>
       </c>
       <c r="AU16" t="n">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="17">
@@ -2990,7 +2990,7 @@
         <v>6.27</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.15</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="19">
@@ -3135,7 +3135,7 @@
         <v>136.44</v>
       </c>
       <c r="AU19" t="n">
-        <v>138.81</v>
+        <v>137.52</v>
       </c>
     </row>
     <row r="20">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU20"/>
+  <dimension ref="A1:AV20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,6 +659,11 @@
           <t>2026-04-10</t>
         </is>
       </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -802,6 +807,9 @@
         <v>4441</v>
       </c>
       <c r="AU2" t="n">
+        <v>4441</v>
+      </c>
+      <c r="AV2" t="n">
         <v>4441</v>
       </c>
     </row>
@@ -919,6 +927,9 @@
       <c r="AU3" t="n">
         <v>559</v>
       </c>
+      <c r="AV3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1064,6 +1075,9 @@
       <c r="AU4" t="n">
         <v>1788</v>
       </c>
+      <c r="AV4" t="n">
+        <v>1788</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1207,6 +1221,9 @@
         <v>732</v>
       </c>
       <c r="AU5" t="n">
+        <v>724</v>
+      </c>
+      <c r="AV5" t="n">
         <v>724</v>
       </c>
     </row>
@@ -1324,6 +1341,9 @@
       <c r="AU6" t="n">
         <v>2</v>
       </c>
+      <c r="AV6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1467,6 +1487,9 @@
         <v>3</v>
       </c>
       <c r="AU7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1584,6 +1607,9 @@
       <c r="AU8" t="n">
         <v>19</v>
       </c>
+      <c r="AV8" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1699,6 +1725,9 @@
       <c r="AU9" t="n">
         <v>2</v>
       </c>
+      <c r="AV9" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1844,6 +1873,9 @@
       <c r="AU10" t="n">
         <v>1283</v>
       </c>
+      <c r="AV10" t="n">
+        <v>1283</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1989,6 +2021,9 @@
       <c r="AU11" t="n">
         <v>61</v>
       </c>
+      <c r="AV11" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -2134,6 +2169,9 @@
       <c r="AU12" t="n">
         <v>3</v>
       </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -2273,6 +2311,7 @@
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr"/>
       <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -2412,6 +2451,7 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr"/>
       <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -2557,6 +2597,9 @@
       <c r="AU15" t="n">
         <v>64</v>
       </c>
+      <c r="AV15" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -2702,6 +2745,9 @@
       <c r="AU16" t="n">
         <v>852</v>
       </c>
+      <c r="AV16" t="n">
+        <v>852</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -2847,6 +2893,9 @@
       <c r="AU17" t="n">
         <v>1536</v>
       </c>
+      <c r="AV17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -2992,6 +3041,9 @@
       <c r="AU18" t="n">
         <v>6.2</v>
       </c>
+      <c r="AV18" t="n">
+        <v>6.06</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -3137,6 +3189,9 @@
       <c r="AU19" t="n">
         <v>137.52</v>
       </c>
+      <c r="AV19" t="n">
+        <v>140.51</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -3372,6 +3427,11 @@
       <c r="AU20" t="inlineStr">
         <is>
           <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV20"/>
+  <dimension ref="A1:AW20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -664,6 +664,11 @@
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -811,6 +816,9 @@
       </c>
       <c r="AV2" t="n">
         <v>4441</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>4440</v>
       </c>
     </row>
     <row r="3">
@@ -930,6 +938,9 @@
       <c r="AV3" t="n">
         <v>559</v>
       </c>
+      <c r="AW3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1078,6 +1089,9 @@
       <c r="AV4" t="n">
         <v>1788</v>
       </c>
+      <c r="AW4" t="n">
+        <v>1787</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1225,6 +1239,9 @@
       </c>
       <c r="AV5" t="n">
         <v>724</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>723</v>
       </c>
     </row>
     <row r="6">
@@ -1344,6 +1361,9 @@
       <c r="AV6" t="n">
         <v>2</v>
       </c>
+      <c r="AW6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1490,6 +1510,9 @@
         <v>3</v>
       </c>
       <c r="AV7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1610,6 +1633,9 @@
       <c r="AV8" t="n">
         <v>19</v>
       </c>
+      <c r="AW8" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1728,6 +1754,9 @@
       <c r="AV9" t="n">
         <v>2</v>
       </c>
+      <c r="AW9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1876,6 +1905,9 @@
       <c r="AV10" t="n">
         <v>1283</v>
       </c>
+      <c r="AW10" t="n">
+        <v>1283</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -2024,6 +2056,9 @@
       <c r="AV11" t="n">
         <v>61</v>
       </c>
+      <c r="AW11" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -2170,6 +2205,9 @@
         <v>3</v>
       </c>
       <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2312,6 +2350,7 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AU13" t="inlineStr"/>
       <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -2452,6 +2491,7 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AU14" t="inlineStr"/>
       <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -2600,6 +2640,9 @@
       <c r="AV15" t="n">
         <v>64</v>
       </c>
+      <c r="AW15" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -2748,6 +2791,9 @@
       <c r="AV16" t="n">
         <v>852</v>
       </c>
+      <c r="AW16" t="n">
+        <v>851</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -2896,6 +2942,9 @@
       <c r="AV17" t="n">
         <v>1536</v>
       </c>
+      <c r="AW17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -3044,6 +3093,9 @@
       <c r="AV18" t="n">
         <v>6.06</v>
       </c>
+      <c r="AW18" t="n">
+        <v>5.94</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -3192,6 +3244,9 @@
       <c r="AV19" t="n">
         <v>140.51</v>
       </c>
+      <c r="AW19" t="n">
+        <v>143.33</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -3432,6 +3487,11 @@
       <c r="AV20" t="inlineStr">
         <is>
           <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,253 +413,258 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW20"/>
+  <dimension ref="A1:AX20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>2026-02-24</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>2026-02-27</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>2026-03-03</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>2026-03-28</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>2026-04-04</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>2026-04-05</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>2026-04-07</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
@@ -820,9 +813,12 @@
       <c r="AW2" t="n">
         <v>4440</v>
       </c>
+      <c r="AX2" t="n">
+        <v>4442</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>ACCOLTO</t>
         </is>
@@ -941,9 +937,12 @@
       <c r="AW3" t="n">
         <v>559</v>
       </c>
+      <c r="AX3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>ASSEGNATO A GIUDICE</t>
         </is>
@@ -1092,9 +1091,12 @@
       <c r="AW4" t="n">
         <v>1787</v>
       </c>
+      <c r="AX4" t="n">
+        <v>1789</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>ATTESA DEPOSITO NOTE IN SOSTITUZIONE UDIENZA</t>
         </is>
@@ -1243,9 +1245,12 @@
       <c r="AW5" t="n">
         <v>723</v>
       </c>
+      <c r="AX5" t="n">
+        <v>723</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>ATTESA DEPOSITO PROVVEDIMENTI</t>
         </is>
@@ -1364,9 +1369,12 @@
       <c r="AW6" t="n">
         <v>2</v>
       </c>
+      <c r="AX6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>ATTESA ESITO UDIENZA DI COMPARIZIONE</t>
         </is>
@@ -1515,9 +1523,12 @@
       <c r="AW7" t="n">
         <v>3</v>
       </c>
+      <c r="AX7" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>ESTINTO</t>
         </is>
@@ -1636,9 +1647,12 @@
       <c r="AW8" t="n">
         <v>19</v>
       </c>
+      <c r="AX8" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>INCOMPETENTE</t>
         </is>
@@ -1757,9 +1771,12 @@
       <c r="AW9" t="n">
         <v>3</v>
       </c>
+      <c r="AX9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>PROCEDIMENTO DEFINITO</t>
         </is>
@@ -1908,9 +1925,12 @@
       <c r="AW10" t="n">
         <v>1283</v>
       </c>
+      <c r="AX10" t="n">
+        <v>1283</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>RISERVATO</t>
         </is>
@@ -2059,9 +2079,12 @@
       <c r="AW11" t="n">
         <v>61</v>
       </c>
+      <c r="AX11" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Sentenças do dia</t>
         </is>
@@ -2210,9 +2233,12 @@
       <c r="AW12" t="n">
         <v>0</v>
       </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Processos agendados presencial 2023</t>
         </is>
@@ -2351,9 +2377,10 @@
       <c r="AU13" t="inlineStr"/>
       <c r="AV13" t="inlineStr"/>
       <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Processos agendados presencial 2024</t>
         </is>
@@ -2492,9 +2519,10 @@
       <c r="AU14" t="inlineStr"/>
       <c r="AV14" t="inlineStr"/>
       <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Fila para marcação 704/2025</t>
         </is>
@@ -2643,9 +2671,12 @@
       <c r="AW15" t="n">
         <v>64</v>
       </c>
+      <c r="AX15" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fila para sentença</t>
         </is>
@@ -2794,9 +2825,12 @@
       <c r="AW16" t="n">
         <v>851</v>
       </c>
+      <c r="AX16" t="n">
+        <v>851</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Processos de 2025</t>
         </is>
@@ -2945,9 +2979,12 @@
       <c r="AW17" t="n">
         <v>1536</v>
       </c>
+      <c r="AX17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Média sentenças diárias</t>
         </is>
@@ -3096,9 +3133,12 @@
       <c r="AW18" t="n">
         <v>5.94</v>
       </c>
+      <c r="AX18" t="n">
+        <v>5.82</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Dias para sentença</t>
         </is>
@@ -3247,9 +3287,12 @@
       <c r="AW19" t="n">
         <v>143.33</v>
       </c>
+      <c r="AX19" t="n">
+        <v>146.31</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Data estimada sentença</t>
         </is>
@@ -3492,6 +3535,11 @@
       <c r="AW20" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX20"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,6 +662,11 @@
           <t>2026-04-14</t>
         </is>
       </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -815,6 +820,9 @@
       </c>
       <c r="AX2" t="n">
         <v>4442</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>4443</v>
       </c>
     </row>
     <row r="3">
@@ -940,6 +948,9 @@
       <c r="AX3" t="n">
         <v>559</v>
       </c>
+      <c r="AY3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1094,6 +1105,9 @@
       <c r="AX4" t="n">
         <v>1789</v>
       </c>
+      <c r="AY4" t="n">
+        <v>1790</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1246,6 +1260,9 @@
         <v>723</v>
       </c>
       <c r="AX5" t="n">
+        <v>723</v>
+      </c>
+      <c r="AY5" t="n">
         <v>723</v>
       </c>
     </row>
@@ -1372,6 +1389,9 @@
       <c r="AX6" t="n">
         <v>2</v>
       </c>
+      <c r="AY6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1524,6 +1544,9 @@
         <v>3</v>
       </c>
       <c r="AX7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1650,6 +1673,9 @@
       <c r="AX8" t="n">
         <v>19</v>
       </c>
+      <c r="AY8" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1774,6 +1800,9 @@
       <c r="AX9" t="n">
         <v>3</v>
       </c>
+      <c r="AY9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1928,6 +1957,9 @@
       <c r="AX10" t="n">
         <v>1283</v>
       </c>
+      <c r="AY10" t="n">
+        <v>1283</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2082,6 +2114,9 @@
       <c r="AX11" t="n">
         <v>61</v>
       </c>
+      <c r="AY11" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2234,6 +2269,9 @@
         <v>0</v>
       </c>
       <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2378,6 +2416,7 @@
       <c r="AV13" t="inlineStr"/>
       <c r="AW13" t="inlineStr"/>
       <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2520,6 +2559,7 @@
       <c r="AV14" t="inlineStr"/>
       <c r="AW14" t="inlineStr"/>
       <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2674,6 +2714,9 @@
       <c r="AX15" t="n">
         <v>64</v>
       </c>
+      <c r="AY15" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2828,6 +2871,9 @@
       <c r="AX16" t="n">
         <v>851</v>
       </c>
+      <c r="AY16" t="n">
+        <v>851</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2982,6 +3028,9 @@
       <c r="AX17" t="n">
         <v>1536</v>
       </c>
+      <c r="AY17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3136,6 +3185,9 @@
       <c r="AX18" t="n">
         <v>5.82</v>
       </c>
+      <c r="AY18" t="n">
+        <v>5.7</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3290,6 +3342,9 @@
       <c r="AX19" t="n">
         <v>146.31</v>
       </c>
+      <c r="AY19" t="n">
+        <v>149.3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3540,6 +3595,11 @@
       <c r="AX20" t="inlineStr">
         <is>
           <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -1263,7 +1263,7 @@
         <v>723</v>
       </c>
       <c r="AY5" t="n">
-        <v>723</v>
+        <v>719</v>
       </c>
     </row>
     <row r="6">
@@ -1958,7 +1958,7 @@
         <v>1283</v>
       </c>
       <c r="AY10" t="n">
-        <v>1283</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="11">
@@ -2115,7 +2115,7 @@
         <v>61</v>
       </c>
       <c r="AY11" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12">
@@ -2272,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -2872,7 +2872,7 @@
         <v>851</v>
       </c>
       <c r="AY16" t="n">
-        <v>851</v>
+        <v>843</v>
       </c>
     </row>
     <row r="17">
@@ -3186,7 +3186,7 @@
         <v>5.82</v>
       </c>
       <c r="AY18" t="n">
-        <v>5.7</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="19">
@@ -3343,7 +3343,7 @@
         <v>146.31</v>
       </c>
       <c r="AY19" t="n">
-        <v>149.3</v>
+        <v>143.86</v>
       </c>
     </row>
     <row r="20">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,6 +667,11 @@
           <t>2026-04-15</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -822,6 +827,9 @@
         <v>4442</v>
       </c>
       <c r="AY2" t="n">
+        <v>4443</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>4443</v>
       </c>
     </row>
@@ -951,6 +959,9 @@
       <c r="AY3" t="n">
         <v>559</v>
       </c>
+      <c r="AZ3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1108,6 +1119,9 @@
       <c r="AY4" t="n">
         <v>1790</v>
       </c>
+      <c r="AZ4" t="n">
+        <v>1790</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1264,6 +1278,9 @@
       </c>
       <c r="AY5" t="n">
         <v>719</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>708</v>
       </c>
     </row>
     <row r="6">
@@ -1392,6 +1409,9 @@
       <c r="AY6" t="n">
         <v>2</v>
       </c>
+      <c r="AZ6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1547,6 +1567,9 @@
         <v>3</v>
       </c>
       <c r="AY7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1676,6 +1699,9 @@
       <c r="AY8" t="n">
         <v>19</v>
       </c>
+      <c r="AZ8" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1803,6 +1829,9 @@
       <c r="AY9" t="n">
         <v>3</v>
       </c>
+      <c r="AZ9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1960,6 +1989,9 @@
       <c r="AY10" t="n">
         <v>1291</v>
       </c>
+      <c r="AZ10" t="n">
+        <v>1295</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2117,6 +2149,9 @@
       <c r="AY11" t="n">
         <v>57</v>
       </c>
+      <c r="AZ11" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2273,6 +2308,9 @@
       </c>
       <c r="AY12" t="n">
         <v>8</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -2417,6 +2455,7 @@
       <c r="AW13" t="inlineStr"/>
       <c r="AX13" t="inlineStr"/>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2560,6 +2599,7 @@
       <c r="AW14" t="inlineStr"/>
       <c r="AX14" t="inlineStr"/>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2717,6 +2757,9 @@
       <c r="AY15" t="n">
         <v>64</v>
       </c>
+      <c r="AZ15" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2874,6 +2917,9 @@
       <c r="AY16" t="n">
         <v>843</v>
       </c>
+      <c r="AZ16" t="n">
+        <v>839</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3031,6 +3077,9 @@
       <c r="AY17" t="n">
         <v>1536</v>
       </c>
+      <c r="AZ17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3188,6 +3237,9 @@
       <c r="AY18" t="n">
         <v>5.86</v>
       </c>
+      <c r="AZ18" t="n">
+        <v>5.82</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3345,6 +3397,9 @@
       <c r="AY19" t="n">
         <v>143.86</v>
       </c>
+      <c r="AZ19" t="n">
+        <v>144.07</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3600,6 +3655,11 @@
       <c r="AY20" t="inlineStr">
         <is>
           <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:BA20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>2026-04-16</t>
         </is>
       </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -830,6 +835,9 @@
         <v>4443</v>
       </c>
       <c r="AZ2" t="n">
+        <v>4443</v>
+      </c>
+      <c r="BA2" t="n">
         <v>4443</v>
       </c>
     </row>
@@ -962,6 +970,9 @@
       <c r="AZ3" t="n">
         <v>559</v>
       </c>
+      <c r="BA3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1122,6 +1133,9 @@
       <c r="AZ4" t="n">
         <v>1790</v>
       </c>
+      <c r="BA4" t="n">
+        <v>1790</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1280,6 +1294,9 @@
         <v>719</v>
       </c>
       <c r="AZ5" t="n">
+        <v>708</v>
+      </c>
+      <c r="BA5" t="n">
         <v>708</v>
       </c>
     </row>
@@ -1412,6 +1429,9 @@
       <c r="AZ6" t="n">
         <v>2</v>
       </c>
+      <c r="BA6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1570,6 +1590,9 @@
         <v>3</v>
       </c>
       <c r="AZ7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1702,6 +1725,9 @@
       <c r="AZ8" t="n">
         <v>19</v>
       </c>
+      <c r="BA8" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1832,6 +1858,9 @@
       <c r="AZ9" t="n">
         <v>3</v>
       </c>
+      <c r="BA9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1992,6 +2021,9 @@
       <c r="AZ10" t="n">
         <v>1295</v>
       </c>
+      <c r="BA10" t="n">
+        <v>1295</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2152,6 +2184,9 @@
       <c r="AZ11" t="n">
         <v>64</v>
       </c>
+      <c r="BA11" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2311,6 +2346,9 @@
       </c>
       <c r="AZ12" t="n">
         <v>4</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2456,6 +2494,7 @@
       <c r="AX13" t="inlineStr"/>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2600,6 +2639,7 @@
       <c r="AX14" t="inlineStr"/>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2760,6 +2800,9 @@
       <c r="AZ15" t="n">
         <v>64</v>
       </c>
+      <c r="BA15" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2920,6 +2963,9 @@
       <c r="AZ16" t="n">
         <v>839</v>
       </c>
+      <c r="BA16" t="n">
+        <v>839</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3080,6 +3126,9 @@
       <c r="AZ17" t="n">
         <v>1536</v>
       </c>
+      <c r="BA17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3240,6 +3289,9 @@
       <c r="AZ18" t="n">
         <v>5.82</v>
       </c>
+      <c r="BA18" t="n">
+        <v>5.71</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3400,6 +3452,9 @@
       <c r="AZ19" t="n">
         <v>144.07</v>
       </c>
+      <c r="BA19" t="n">
+        <v>146.9</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3660,6 +3715,11 @@
       <c r="AZ20" t="inlineStr">
         <is>
           <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA20"/>
+  <dimension ref="A1:BB20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -677,6 +677,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -838,6 +843,9 @@
         <v>4443</v>
       </c>
       <c r="BA2" t="n">
+        <v>4443</v>
+      </c>
+      <c r="BB2" t="n">
         <v>4443</v>
       </c>
     </row>
@@ -973,6 +981,9 @@
       <c r="BA3" t="n">
         <v>559</v>
       </c>
+      <c r="BB3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1136,6 +1147,9 @@
       <c r="BA4" t="n">
         <v>1790</v>
       </c>
+      <c r="BB4" t="n">
+        <v>1790</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1297,6 +1311,9 @@
         <v>708</v>
       </c>
       <c r="BA5" t="n">
+        <v>708</v>
+      </c>
+      <c r="BB5" t="n">
         <v>708</v>
       </c>
     </row>
@@ -1432,6 +1449,9 @@
       <c r="BA6" t="n">
         <v>2</v>
       </c>
+      <c r="BB6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1593,6 +1613,9 @@
         <v>3</v>
       </c>
       <c r="BA7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1728,6 +1751,9 @@
       <c r="BA8" t="n">
         <v>19</v>
       </c>
+      <c r="BB8" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1861,6 +1887,9 @@
       <c r="BA9" t="n">
         <v>3</v>
       </c>
+      <c r="BB9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2024,6 +2053,9 @@
       <c r="BA10" t="n">
         <v>1295</v>
       </c>
+      <c r="BB10" t="n">
+        <v>1295</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2187,6 +2219,9 @@
       <c r="BA11" t="n">
         <v>64</v>
       </c>
+      <c r="BB11" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2348,6 +2383,9 @@
         <v>4</v>
       </c>
       <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2495,6 +2533,7 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2640,6 +2679,7 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr"/>
       <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2803,6 +2843,9 @@
       <c r="BA15" t="n">
         <v>64</v>
       </c>
+      <c r="BB15" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2966,6 +3009,9 @@
       <c r="BA16" t="n">
         <v>839</v>
       </c>
+      <c r="BB16" t="n">
+        <v>839</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3129,6 +3175,9 @@
       <c r="BA17" t="n">
         <v>1536</v>
       </c>
+      <c r="BB17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3292,6 +3341,9 @@
       <c r="BA18" t="n">
         <v>5.71</v>
       </c>
+      <c r="BB18" t="n">
+        <v>5.6</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3455,6 +3507,9 @@
       <c r="BA19" t="n">
         <v>146.9</v>
       </c>
+      <c r="BB19" t="n">
+        <v>149.72</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3720,6 +3775,11 @@
       <c r="BA20" t="inlineStr">
         <is>
           <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -846,7 +846,7 @@
         <v>4443</v>
       </c>
       <c r="BB2" t="n">
-        <v>4443</v>
+        <v>4444</v>
       </c>
     </row>
     <row r="3">
@@ -1148,7 +1148,7 @@
         <v>1790</v>
       </c>
       <c r="BB4" t="n">
-        <v>1790</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="5">
@@ -1314,7 +1314,7 @@
         <v>708</v>
       </c>
       <c r="BB5" t="n">
-        <v>708</v>
+        <v>696</v>
       </c>
     </row>
     <row r="6">
@@ -2054,7 +2054,7 @@
         <v>1295</v>
       </c>
       <c r="BB10" t="n">
-        <v>1295</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="11">
@@ -2220,7 +2220,7 @@
         <v>64</v>
       </c>
       <c r="BB11" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
@@ -2386,7 +2386,7 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -2844,7 +2844,7 @@
         <v>64</v>
       </c>
       <c r="BB15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16">
@@ -3010,7 +3010,7 @@
         <v>839</v>
       </c>
       <c r="BB16" t="n">
-        <v>839</v>
+        <v>824</v>
       </c>
     </row>
     <row r="17">
@@ -3342,7 +3342,7 @@
         <v>5.71</v>
       </c>
       <c r="BB18" t="n">
-        <v>5.6</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="19">
@@ -3508,7 +3508,7 @@
         <v>146.9</v>
       </c>
       <c r="BB19" t="n">
-        <v>149.72</v>
+        <v>139.53</v>
       </c>
     </row>
     <row r="20">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB20"/>
+  <dimension ref="A1:BC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -682,6 +682,11 @@
           <t>2026-04-18</t>
         </is>
       </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -846,6 +851,9 @@
         <v>4443</v>
       </c>
       <c r="BB2" t="n">
+        <v>4444</v>
+      </c>
+      <c r="BC2" t="n">
         <v>4444</v>
       </c>
     </row>
@@ -984,6 +992,9 @@
       <c r="BB3" t="n">
         <v>559</v>
       </c>
+      <c r="BC3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1150,6 +1161,9 @@
       <c r="BB4" t="n">
         <v>1791</v>
       </c>
+      <c r="BC4" t="n">
+        <v>1791</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1315,6 +1329,9 @@
       </c>
       <c r="BB5" t="n">
         <v>696</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>694</v>
       </c>
     </row>
     <row r="6">
@@ -1452,6 +1469,9 @@
       <c r="BB6" t="n">
         <v>2</v>
       </c>
+      <c r="BC6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1616,6 +1636,9 @@
         <v>3</v>
       </c>
       <c r="BB7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1754,6 +1777,9 @@
       <c r="BB8" t="n">
         <v>19</v>
       </c>
+      <c r="BC8" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1890,6 +1916,9 @@
       <c r="BB9" t="n">
         <v>3</v>
       </c>
+      <c r="BC9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2056,6 +2085,9 @@
       <c r="BB10" t="n">
         <v>1311</v>
       </c>
+      <c r="BC10" t="n">
+        <v>1322</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2222,6 +2254,9 @@
       <c r="BB11" t="n">
         <v>60</v>
       </c>
+      <c r="BC11" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2387,6 +2422,9 @@
       </c>
       <c r="BB12" t="n">
         <v>16</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -2534,6 +2572,7 @@
       <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2680,6 +2719,7 @@
       <c r="AZ14" t="inlineStr"/>
       <c r="BA14" t="inlineStr"/>
       <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2846,6 +2886,9 @@
       <c r="BB15" t="n">
         <v>65</v>
       </c>
+      <c r="BC15" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3012,6 +3055,9 @@
       <c r="BB16" t="n">
         <v>824</v>
       </c>
+      <c r="BC16" t="n">
+        <v>813</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3178,6 +3224,9 @@
       <c r="BB17" t="n">
         <v>1536</v>
       </c>
+      <c r="BC17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3344,6 +3393,9 @@
       <c r="BB18" t="n">
         <v>5.91</v>
       </c>
+      <c r="BC18" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3510,6 +3562,9 @@
       <c r="BB19" t="n">
         <v>139.53</v>
       </c>
+      <c r="BC19" t="n">
+        <v>135.5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3780,6 +3835,11 @@
       <c r="BB20" t="inlineStr">
         <is>
           <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC20"/>
+  <dimension ref="A1:BD20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -687,6 +687,11 @@
           <t>2026-04-19</t>
         </is>
       </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -854,6 +859,9 @@
         <v>4444</v>
       </c>
       <c r="BC2" t="n">
+        <v>4444</v>
+      </c>
+      <c r="BD2" t="n">
         <v>4444</v>
       </c>
     </row>
@@ -995,6 +1003,9 @@
       <c r="BC3" t="n">
         <v>559</v>
       </c>
+      <c r="BD3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1164,6 +1175,9 @@
       <c r="BC4" t="n">
         <v>1791</v>
       </c>
+      <c r="BD4" t="n">
+        <v>1791</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1331,6 +1345,9 @@
         <v>696</v>
       </c>
       <c r="BC5" t="n">
+        <v>694</v>
+      </c>
+      <c r="BD5" t="n">
         <v>694</v>
       </c>
     </row>
@@ -1472,6 +1489,9 @@
       <c r="BC6" t="n">
         <v>2</v>
       </c>
+      <c r="BD6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1639,6 +1659,9 @@
         <v>3</v>
       </c>
       <c r="BC7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1780,6 +1803,9 @@
       <c r="BC8" t="n">
         <v>19</v>
       </c>
+      <c r="BD8" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1919,6 +1945,9 @@
       <c r="BC9" t="n">
         <v>3</v>
       </c>
+      <c r="BD9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2088,6 +2117,9 @@
       <c r="BC10" t="n">
         <v>1322</v>
       </c>
+      <c r="BD10" t="n">
+        <v>1322</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2257,6 +2289,9 @@
       <c r="BC11" t="n">
         <v>51</v>
       </c>
+      <c r="BD11" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2425,6 +2460,9 @@
       </c>
       <c r="BC12" t="n">
         <v>11</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2573,6 +2611,7 @@
       <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2720,6 +2759,7 @@
       <c r="BA14" t="inlineStr"/>
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2889,6 +2929,9 @@
       <c r="BC15" t="n">
         <v>65</v>
       </c>
+      <c r="BD15" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3058,6 +3101,9 @@
       <c r="BC16" t="n">
         <v>813</v>
       </c>
+      <c r="BD16" t="n">
+        <v>813</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3227,6 +3273,9 @@
       <c r="BC17" t="n">
         <v>1536</v>
       </c>
+      <c r="BD17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3396,6 +3445,9 @@
       <c r="BC18" t="n">
         <v>6</v>
       </c>
+      <c r="BD18" t="n">
+        <v>5.89</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3565,6 +3617,9 @@
       <c r="BC19" t="n">
         <v>135.5</v>
       </c>
+      <c r="BD19" t="n">
+        <v>138.01</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3840,6 +3895,11 @@
       <c r="BC20" t="inlineStr">
         <is>
           <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD20"/>
+  <dimension ref="A1:BE20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,6 +692,11 @@
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -862,6 +867,9 @@
         <v>4444</v>
       </c>
       <c r="BD2" t="n">
+        <v>4444</v>
+      </c>
+      <c r="BE2" t="n">
         <v>4444</v>
       </c>
     </row>
@@ -1006,6 +1014,9 @@
       <c r="BD3" t="n">
         <v>559</v>
       </c>
+      <c r="BE3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1178,6 +1189,9 @@
       <c r="BD4" t="n">
         <v>1791</v>
       </c>
+      <c r="BE4" t="n">
+        <v>1791</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1348,6 +1362,9 @@
         <v>694</v>
       </c>
       <c r="BD5" t="n">
+        <v>694</v>
+      </c>
+      <c r="BE5" t="n">
         <v>694</v>
       </c>
     </row>
@@ -1492,6 +1509,9 @@
       <c r="BD6" t="n">
         <v>2</v>
       </c>
+      <c r="BE6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1662,6 +1682,9 @@
         <v>3</v>
       </c>
       <c r="BD7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1806,6 +1829,9 @@
       <c r="BD8" t="n">
         <v>19</v>
       </c>
+      <c r="BE8" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1948,6 +1974,9 @@
       <c r="BD9" t="n">
         <v>3</v>
       </c>
+      <c r="BE9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2120,6 +2149,9 @@
       <c r="BD10" t="n">
         <v>1322</v>
       </c>
+      <c r="BE10" t="n">
+        <v>1322</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2292,6 +2324,9 @@
       <c r="BD11" t="n">
         <v>51</v>
       </c>
+      <c r="BE11" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2462,6 +2497,9 @@
         <v>11</v>
       </c>
       <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2612,6 +2650,7 @@
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
       <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2760,6 +2799,7 @@
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="inlineStr"/>
       <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2932,6 +2972,9 @@
       <c r="BD15" t="n">
         <v>65</v>
       </c>
+      <c r="BE15" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3104,6 +3147,9 @@
       <c r="BD16" t="n">
         <v>813</v>
       </c>
+      <c r="BE16" t="n">
+        <v>813</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3276,6 +3322,9 @@
       <c r="BD17" t="n">
         <v>1536</v>
       </c>
+      <c r="BE17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3448,6 +3497,9 @@
       <c r="BD18" t="n">
         <v>5.89</v>
       </c>
+      <c r="BE18" t="n">
+        <v>5.79</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3620,6 +3672,9 @@
       <c r="BD19" t="n">
         <v>138.01</v>
       </c>
+      <c r="BE19" t="n">
+        <v>140.52</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3900,6 +3955,11 @@
       <c r="BD20" t="inlineStr">
         <is>
           <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE20"/>
+  <dimension ref="A1:BF20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -697,6 +697,11 @@
           <t>2026-04-21</t>
         </is>
       </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -871,6 +876,9 @@
       </c>
       <c r="BE2" t="n">
         <v>4444</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>4457</v>
       </c>
     </row>
     <row r="3">
@@ -1017,6 +1025,9 @@
       <c r="BE3" t="n">
         <v>559</v>
       </c>
+      <c r="BF3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1192,6 +1203,9 @@
       <c r="BE4" t="n">
         <v>1791</v>
       </c>
+      <c r="BF4" t="n">
+        <v>1804</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1366,6 +1380,9 @@
       </c>
       <c r="BE5" t="n">
         <v>694</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>695</v>
       </c>
     </row>
     <row r="6">
@@ -1512,6 +1529,9 @@
       <c r="BE6" t="n">
         <v>2</v>
       </c>
+      <c r="BF6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1685,6 +1705,9 @@
         <v>3</v>
       </c>
       <c r="BE7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1832,6 +1855,9 @@
       <c r="BE8" t="n">
         <v>19</v>
       </c>
+      <c r="BF8" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1977,6 +2003,9 @@
       <c r="BE9" t="n">
         <v>3</v>
       </c>
+      <c r="BF9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2152,6 +2181,9 @@
       <c r="BE10" t="n">
         <v>1322</v>
       </c>
+      <c r="BF10" t="n">
+        <v>1330</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2327,6 +2359,9 @@
       <c r="BE11" t="n">
         <v>51</v>
       </c>
+      <c r="BF11" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2501,6 +2536,9 @@
       </c>
       <c r="BE12" t="n">
         <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -2651,6 +2689,7 @@
       <c r="BC13" t="inlineStr"/>
       <c r="BD13" t="inlineStr"/>
       <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2800,6 +2839,7 @@
       <c r="BC14" t="inlineStr"/>
       <c r="BD14" t="inlineStr"/>
       <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2975,6 +3015,9 @@
       <c r="BE15" t="n">
         <v>65</v>
       </c>
+      <c r="BF15" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3150,6 +3193,9 @@
       <c r="BE16" t="n">
         <v>813</v>
       </c>
+      <c r="BF16" t="n">
+        <v>805</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3325,6 +3371,9 @@
       <c r="BE17" t="n">
         <v>1536</v>
       </c>
+      <c r="BF17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3500,6 +3549,9 @@
       <c r="BE18" t="n">
         <v>5.79</v>
       </c>
+      <c r="BF18" t="n">
+        <v>5.82</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3675,6 +3727,9 @@
       <c r="BE19" t="n">
         <v>140.52</v>
       </c>
+      <c r="BF19" t="n">
+        <v>138.21</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3960,6 +4015,11 @@
       <c r="BE20" t="inlineStr">
         <is>
           <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF20"/>
+  <dimension ref="A1:BG20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,6 +702,11 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -879,6 +884,9 @@
       </c>
       <c r="BF2" t="n">
         <v>4457</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>4407</v>
       </c>
     </row>
     <row r="3">
@@ -1028,6 +1036,9 @@
       <c r="BF3" t="n">
         <v>559</v>
       </c>
+      <c r="BG3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1206,6 +1217,9 @@
       <c r="BF4" t="n">
         <v>1804</v>
       </c>
+      <c r="BG4" t="n">
+        <v>1804</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1383,6 +1397,9 @@
       </c>
       <c r="BF5" t="n">
         <v>695</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>645</v>
       </c>
     </row>
     <row r="6">
@@ -1532,6 +1549,9 @@
       <c r="BF6" t="n">
         <v>2</v>
       </c>
+      <c r="BG6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1708,6 +1728,9 @@
         <v>3</v>
       </c>
       <c r="BF7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1858,6 +1881,9 @@
       <c r="BF8" t="n">
         <v>19</v>
       </c>
+      <c r="BG8" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2006,6 +2032,9 @@
       <c r="BF9" t="n">
         <v>3</v>
       </c>
+      <c r="BG9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2184,6 +2213,9 @@
       <c r="BF10" t="n">
         <v>1330</v>
       </c>
+      <c r="BG10" t="n">
+        <v>1337</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2362,6 +2394,9 @@
       <c r="BF11" t="n">
         <v>42</v>
       </c>
+      <c r="BG11" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2539,6 +2574,9 @@
       </c>
       <c r="BF12" t="n">
         <v>8</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -2690,6 +2728,7 @@
       <c r="BD13" t="inlineStr"/>
       <c r="BE13" t="inlineStr"/>
       <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2840,6 +2879,7 @@
       <c r="BD14" t="inlineStr"/>
       <c r="BE14" t="inlineStr"/>
       <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3018,6 +3058,9 @@
       <c r="BF15" t="n">
         <v>65</v>
       </c>
+      <c r="BG15" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3196,6 +3239,9 @@
       <c r="BF16" t="n">
         <v>805</v>
       </c>
+      <c r="BG16" t="n">
+        <v>748</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3374,6 +3420,9 @@
       <c r="BF17" t="n">
         <v>1536</v>
       </c>
+      <c r="BG17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3552,6 +3601,9 @@
       <c r="BF18" t="n">
         <v>5.82</v>
       </c>
+      <c r="BG18" t="n">
+        <v>5.84</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3730,6 +3782,9 @@
       <c r="BF19" t="n">
         <v>138.21</v>
       </c>
+      <c r="BG19" t="n">
+        <v>127.98</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4020,6 +4075,11 @@
       <c r="BF20" t="inlineStr">
         <is>
           <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG20"/>
+  <dimension ref="A1:BH20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,6 +707,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -886,6 +891,9 @@
         <v>4457</v>
       </c>
       <c r="BG2" t="n">
+        <v>4407</v>
+      </c>
+      <c r="BH2" t="n">
         <v>4407</v>
       </c>
     </row>
@@ -1039,6 +1047,9 @@
       <c r="BG3" t="n">
         <v>559</v>
       </c>
+      <c r="BH3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1220,6 +1231,9 @@
       <c r="BG4" t="n">
         <v>1804</v>
       </c>
+      <c r="BH4" t="n">
+        <v>1802</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1400,6 +1414,9 @@
       </c>
       <c r="BG5" t="n">
         <v>645</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>647</v>
       </c>
     </row>
     <row r="6">
@@ -1552,6 +1569,9 @@
       <c r="BG6" t="n">
         <v>2</v>
       </c>
+      <c r="BH6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1731,6 +1751,9 @@
         <v>3</v>
       </c>
       <c r="BG7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1884,6 +1907,9 @@
       <c r="BG8" t="n">
         <v>19</v>
       </c>
+      <c r="BH8" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2035,6 +2061,9 @@
       <c r="BG9" t="n">
         <v>3</v>
       </c>
+      <c r="BH9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2216,6 +2245,9 @@
       <c r="BG10" t="n">
         <v>1337</v>
       </c>
+      <c r="BH10" t="n">
+        <v>1337</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2397,6 +2429,9 @@
       <c r="BG11" t="n">
         <v>35</v>
       </c>
+      <c r="BH11" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2577,6 +2612,9 @@
       </c>
       <c r="BG12" t="n">
         <v>7</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2729,6 +2767,7 @@
       <c r="BE13" t="inlineStr"/>
       <c r="BF13" t="inlineStr"/>
       <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2880,6 +2919,7 @@
       <c r="BE14" t="inlineStr"/>
       <c r="BF14" t="inlineStr"/>
       <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3061,6 +3101,9 @@
       <c r="BG15" t="n">
         <v>65</v>
       </c>
+      <c r="BH15" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3242,6 +3285,9 @@
       <c r="BG16" t="n">
         <v>748</v>
       </c>
+      <c r="BH16" t="n">
+        <v>750</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3423,6 +3469,9 @@
       <c r="BG17" t="n">
         <v>1536</v>
       </c>
+      <c r="BH17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3604,6 +3653,9 @@
       <c r="BG18" t="n">
         <v>5.84</v>
       </c>
+      <c r="BH18" t="n">
+        <v>5.75</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3785,6 +3837,9 @@
       <c r="BG19" t="n">
         <v>127.98</v>
       </c>
+      <c r="BH19" t="n">
+        <v>130.53</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4080,6 +4135,11 @@
       <c r="BG20" t="inlineStr">
         <is>
           <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH20"/>
+  <dimension ref="A1:BI20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -712,6 +712,11 @@
           <t>2026-04-24</t>
         </is>
       </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -894,6 +899,9 @@
         <v>4407</v>
       </c>
       <c r="BH2" t="n">
+        <v>4407</v>
+      </c>
+      <c r="BI2" t="n">
         <v>4407</v>
       </c>
     </row>
@@ -1050,6 +1058,9 @@
       <c r="BH3" t="n">
         <v>559</v>
       </c>
+      <c r="BI3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1234,6 +1245,9 @@
       <c r="BH4" t="n">
         <v>1802</v>
       </c>
+      <c r="BI4" t="n">
+        <v>1802</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1417,6 +1431,9 @@
       </c>
       <c r="BH5" t="n">
         <v>647</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>638</v>
       </c>
     </row>
     <row r="6">
@@ -1572,6 +1589,9 @@
       <c r="BH6" t="n">
         <v>2</v>
       </c>
+      <c r="BI6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1755,6 +1775,9 @@
       </c>
       <c r="BH7" t="n">
         <v>3</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1910,6 +1933,9 @@
       <c r="BH8" t="n">
         <v>19</v>
       </c>
+      <c r="BI8" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2064,6 +2090,9 @@
       <c r="BH9" t="n">
         <v>3</v>
       </c>
+      <c r="BI9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2248,6 +2277,9 @@
       <c r="BH10" t="n">
         <v>1337</v>
       </c>
+      <c r="BI10" t="n">
+        <v>1338</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2432,6 +2464,9 @@
       <c r="BH11" t="n">
         <v>35</v>
       </c>
+      <c r="BI11" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2615,6 +2650,9 @@
       </c>
       <c r="BH12" t="n">
         <v>0</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -2768,6 +2806,7 @@
       <c r="BF13" t="inlineStr"/>
       <c r="BG13" t="inlineStr"/>
       <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2920,6 +2959,7 @@
       <c r="BF14" t="inlineStr"/>
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3104,6 +3144,9 @@
       <c r="BH15" t="n">
         <v>65</v>
       </c>
+      <c r="BI15" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3288,6 +3331,9 @@
       <c r="BH16" t="n">
         <v>750</v>
       </c>
+      <c r="BI16" t="n">
+        <v>749</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3472,6 +3518,9 @@
       <c r="BH17" t="n">
         <v>1536</v>
       </c>
+      <c r="BI17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3656,6 +3705,9 @@
       <c r="BH18" t="n">
         <v>5.75</v>
       </c>
+      <c r="BI18" t="n">
+        <v>5.67</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3840,6 +3892,9 @@
       <c r="BH19" t="n">
         <v>130.53</v>
       </c>
+      <c r="BI19" t="n">
+        <v>132.18</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4140,6 +4195,11 @@
       <c r="BH20" t="inlineStr">
         <is>
           <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI20"/>
+  <dimension ref="A1:BJ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -717,6 +717,11 @@
           <t>2026-04-25</t>
         </is>
       </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -902,6 +907,9 @@
         <v>4407</v>
       </c>
       <c r="BI2" t="n">
+        <v>4407</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>4407</v>
       </c>
     </row>
@@ -1061,6 +1069,9 @@
       <c r="BI3" t="n">
         <v>559</v>
       </c>
+      <c r="BJ3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1248,6 +1259,9 @@
       <c r="BI4" t="n">
         <v>1802</v>
       </c>
+      <c r="BJ4" t="n">
+        <v>1802</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1433,6 +1447,9 @@
         <v>647</v>
       </c>
       <c r="BI5" t="n">
+        <v>638</v>
+      </c>
+      <c r="BJ5" t="n">
         <v>638</v>
       </c>
     </row>
@@ -1592,6 +1609,9 @@
       <c r="BI6" t="n">
         <v>2</v>
       </c>
+      <c r="BJ6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1777,6 +1797,9 @@
         <v>3</v>
       </c>
       <c r="BI7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1936,6 +1959,9 @@
       <c r="BI8" t="n">
         <v>19</v>
       </c>
+      <c r="BJ8" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2093,6 +2119,9 @@
       <c r="BI9" t="n">
         <v>3</v>
       </c>
+      <c r="BJ9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2280,6 +2309,9 @@
       <c r="BI10" t="n">
         <v>1338</v>
       </c>
+      <c r="BJ10" t="n">
+        <v>1338</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2467,6 +2499,9 @@
       <c r="BI11" t="n">
         <v>44</v>
       </c>
+      <c r="BJ11" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2653,6 +2688,9 @@
       </c>
       <c r="BI12" t="n">
         <v>1</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2807,6 +2845,7 @@
       <c r="BG13" t="inlineStr"/>
       <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2960,6 +2999,7 @@
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3147,6 +3187,9 @@
       <c r="BI15" t="n">
         <v>65</v>
       </c>
+      <c r="BJ15" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3334,6 +3377,9 @@
       <c r="BI16" t="n">
         <v>749</v>
       </c>
+      <c r="BJ16" t="n">
+        <v>749</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3521,6 +3567,9 @@
       <c r="BI17" t="n">
         <v>1536</v>
       </c>
+      <c r="BJ17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3708,6 +3757,9 @@
       <c r="BI18" t="n">
         <v>5.67</v>
       </c>
+      <c r="BJ18" t="n">
+        <v>5.57</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3895,6 +3947,9 @@
       <c r="BI19" t="n">
         <v>132.18</v>
       </c>
+      <c r="BJ19" t="n">
+        <v>134.38</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4200,6 +4255,11 @@
       <c r="BI20" t="inlineStr">
         <is>
           <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ20"/>
+  <dimension ref="A1:BK20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -722,6 +722,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -910,6 +915,9 @@
         <v>4407</v>
       </c>
       <c r="BJ2" t="n">
+        <v>4407</v>
+      </c>
+      <c r="BK2" t="n">
         <v>4407</v>
       </c>
     </row>
@@ -1072,6 +1080,9 @@
       <c r="BJ3" t="n">
         <v>559</v>
       </c>
+      <c r="BK3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1262,6 +1273,9 @@
       <c r="BJ4" t="n">
         <v>1802</v>
       </c>
+      <c r="BK4" t="n">
+        <v>1802</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1450,6 +1464,9 @@
         <v>638</v>
       </c>
       <c r="BJ5" t="n">
+        <v>638</v>
+      </c>
+      <c r="BK5" t="n">
         <v>638</v>
       </c>
     </row>
@@ -1612,6 +1629,9 @@
       <c r="BJ6" t="n">
         <v>2</v>
       </c>
+      <c r="BK6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1800,6 +1820,9 @@
         <v>2</v>
       </c>
       <c r="BJ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1962,6 +1985,9 @@
       <c r="BJ8" t="n">
         <v>19</v>
       </c>
+      <c r="BK8" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2122,6 +2148,9 @@
       <c r="BJ9" t="n">
         <v>3</v>
       </c>
+      <c r="BK9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2312,6 +2341,9 @@
       <c r="BJ10" t="n">
         <v>1338</v>
       </c>
+      <c r="BK10" t="n">
+        <v>1338</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2502,6 +2534,9 @@
       <c r="BJ11" t="n">
         <v>44</v>
       </c>
+      <c r="BK11" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2690,6 +2725,9 @@
         <v>1</v>
       </c>
       <c r="BJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2846,6 +2884,7 @@
       <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr"/>
       <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3000,6 +3039,7 @@
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr"/>
       <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3190,6 +3230,9 @@
       <c r="BJ15" t="n">
         <v>65</v>
       </c>
+      <c r="BK15" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3380,6 +3423,9 @@
       <c r="BJ16" t="n">
         <v>749</v>
       </c>
+      <c r="BK16" t="n">
+        <v>749</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3570,6 +3616,9 @@
       <c r="BJ17" t="n">
         <v>1536</v>
       </c>
+      <c r="BK17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3760,6 +3809,9 @@
       <c r="BJ18" t="n">
         <v>5.57</v>
       </c>
+      <c r="BK18" t="n">
+        <v>5.48</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3950,6 +4002,9 @@
       <c r="BJ19" t="n">
         <v>134.38</v>
       </c>
+      <c r="BK19" t="n">
+        <v>136.58</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4260,6 +4315,11 @@
       <c r="BJ20" t="inlineStr">
         <is>
           <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK20"/>
+  <dimension ref="A1:BL20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -727,6 +727,11 @@
           <t>2026-04-27</t>
         </is>
       </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -918,6 +923,9 @@
         <v>4407</v>
       </c>
       <c r="BK2" t="n">
+        <v>4407</v>
+      </c>
+      <c r="BL2" t="n">
         <v>4407</v>
       </c>
     </row>
@@ -1083,6 +1091,9 @@
       <c r="BK3" t="n">
         <v>559</v>
       </c>
+      <c r="BL3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1276,6 +1287,9 @@
       <c r="BK4" t="n">
         <v>1802</v>
       </c>
+      <c r="BL4" t="n">
+        <v>1802</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1467,6 +1481,9 @@
         <v>638</v>
       </c>
       <c r="BK5" t="n">
+        <v>638</v>
+      </c>
+      <c r="BL5" t="n">
         <v>638</v>
       </c>
     </row>
@@ -1632,6 +1649,9 @@
       <c r="BK6" t="n">
         <v>2</v>
       </c>
+      <c r="BL6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1823,6 +1843,9 @@
         <v>2</v>
       </c>
       <c r="BK7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1988,6 +2011,9 @@
       <c r="BK8" t="n">
         <v>19</v>
       </c>
+      <c r="BL8" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2151,6 +2177,9 @@
       <c r="BK9" t="n">
         <v>3</v>
       </c>
+      <c r="BL9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2344,6 +2373,9 @@
       <c r="BK10" t="n">
         <v>1338</v>
       </c>
+      <c r="BL10" t="n">
+        <v>1338</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2537,6 +2569,9 @@
       <c r="BK11" t="n">
         <v>44</v>
       </c>
+      <c r="BL11" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2728,6 +2763,9 @@
         <v>0</v>
       </c>
       <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2885,6 +2923,7 @@
       <c r="BI13" t="inlineStr"/>
       <c r="BJ13" t="inlineStr"/>
       <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3040,6 +3079,7 @@
       <c r="BI14" t="inlineStr"/>
       <c r="BJ14" t="inlineStr"/>
       <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3233,6 +3273,9 @@
       <c r="BK15" t="n">
         <v>65</v>
       </c>
+      <c r="BL15" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3426,6 +3469,9 @@
       <c r="BK16" t="n">
         <v>749</v>
       </c>
+      <c r="BL16" t="n">
+        <v>749</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3619,6 +3665,9 @@
       <c r="BK17" t="n">
         <v>1536</v>
       </c>
+      <c r="BL17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3812,6 +3861,9 @@
       <c r="BK18" t="n">
         <v>5.48</v>
       </c>
+      <c r="BL18" t="n">
+        <v>5.4</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4005,6 +4057,9 @@
       <c r="BK19" t="n">
         <v>136.58</v>
       </c>
+      <c r="BL19" t="n">
+        <v>138.79</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4320,6 +4375,11 @@
       <c r="BK20" t="inlineStr">
         <is>
           <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL20"/>
+  <dimension ref="A1:BM20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -732,6 +732,11 @@
           <t>2026-04-28</t>
         </is>
       </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -926,6 +931,9 @@
         <v>4407</v>
       </c>
       <c r="BL2" t="n">
+        <v>4407</v>
+      </c>
+      <c r="BM2" t="n">
         <v>4407</v>
       </c>
     </row>
@@ -1094,6 +1102,9 @@
       <c r="BL3" t="n">
         <v>559</v>
       </c>
+      <c r="BM3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1290,6 +1301,9 @@
       <c r="BL4" t="n">
         <v>1802</v>
       </c>
+      <c r="BM4" t="n">
+        <v>1802</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1484,6 +1498,9 @@
         <v>638</v>
       </c>
       <c r="BL5" t="n">
+        <v>638</v>
+      </c>
+      <c r="BM5" t="n">
         <v>638</v>
       </c>
     </row>
@@ -1652,6 +1669,9 @@
       <c r="BL6" t="n">
         <v>2</v>
       </c>
+      <c r="BM6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1846,6 +1866,9 @@
         <v>2</v>
       </c>
       <c r="BL7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2014,6 +2037,9 @@
       <c r="BL8" t="n">
         <v>19</v>
       </c>
+      <c r="BM8" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2180,6 +2206,9 @@
       <c r="BL9" t="n">
         <v>3</v>
       </c>
+      <c r="BM9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2376,6 +2405,9 @@
       <c r="BL10" t="n">
         <v>1338</v>
       </c>
+      <c r="BM10" t="n">
+        <v>1338</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2572,6 +2604,9 @@
       <c r="BL11" t="n">
         <v>44</v>
       </c>
+      <c r="BM11" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2766,6 +2801,9 @@
         <v>0</v>
       </c>
       <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2924,6 +2962,7 @@
       <c r="BJ13" t="inlineStr"/>
       <c r="BK13" t="inlineStr"/>
       <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3080,6 +3119,7 @@
       <c r="BJ14" t="inlineStr"/>
       <c r="BK14" t="inlineStr"/>
       <c r="BL14" t="inlineStr"/>
+      <c r="BM14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3276,6 +3316,9 @@
       <c r="BL15" t="n">
         <v>65</v>
       </c>
+      <c r="BM15" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3472,6 +3515,9 @@
       <c r="BL16" t="n">
         <v>749</v>
       </c>
+      <c r="BM16" t="n">
+        <v>749</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3668,6 +3714,9 @@
       <c r="BL17" t="n">
         <v>1536</v>
       </c>
+      <c r="BM17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3864,6 +3913,9 @@
       <c r="BL18" t="n">
         <v>5.4</v>
       </c>
+      <c r="BM18" t="n">
+        <v>5.31</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4060,6 +4112,9 @@
       <c r="BL19" t="n">
         <v>138.79</v>
       </c>
+      <c r="BM19" t="n">
+        <v>140.99</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4380,6 +4435,11 @@
       <c r="BL20" t="inlineStr">
         <is>
           <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM20"/>
+  <dimension ref="A1:BN20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -737,6 +737,11 @@
           <t>2026-04-29</t>
         </is>
       </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -934,6 +939,9 @@
         <v>4407</v>
       </c>
       <c r="BM2" t="n">
+        <v>4407</v>
+      </c>
+      <c r="BN2" t="n">
         <v>4407</v>
       </c>
     </row>
@@ -1105,6 +1113,9 @@
       <c r="BM3" t="n">
         <v>559</v>
       </c>
+      <c r="BN3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1304,6 +1315,9 @@
       <c r="BM4" t="n">
         <v>1802</v>
       </c>
+      <c r="BN4" t="n">
+        <v>1802</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1501,6 +1515,9 @@
         <v>638</v>
       </c>
       <c r="BM5" t="n">
+        <v>638</v>
+      </c>
+      <c r="BN5" t="n">
         <v>638</v>
       </c>
     </row>
@@ -1672,6 +1689,9 @@
       <c r="BM6" t="n">
         <v>2</v>
       </c>
+      <c r="BN6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1869,6 +1889,9 @@
         <v>2</v>
       </c>
       <c r="BM7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2040,6 +2063,9 @@
       <c r="BM8" t="n">
         <v>19</v>
       </c>
+      <c r="BN8" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2209,6 +2235,9 @@
       <c r="BM9" t="n">
         <v>3</v>
       </c>
+      <c r="BN9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2408,6 +2437,9 @@
       <c r="BM10" t="n">
         <v>1338</v>
       </c>
+      <c r="BN10" t="n">
+        <v>1338</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2607,6 +2639,9 @@
       <c r="BM11" t="n">
         <v>44</v>
       </c>
+      <c r="BN11" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2804,6 +2839,9 @@
         <v>0</v>
       </c>
       <c r="BM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2963,6 +3001,7 @@
       <c r="BK13" t="inlineStr"/>
       <c r="BL13" t="inlineStr"/>
       <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3120,6 +3159,7 @@
       <c r="BK14" t="inlineStr"/>
       <c r="BL14" t="inlineStr"/>
       <c r="BM14" t="inlineStr"/>
+      <c r="BN14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3319,6 +3359,9 @@
       <c r="BM15" t="n">
         <v>65</v>
       </c>
+      <c r="BN15" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3518,6 +3561,9 @@
       <c r="BM16" t="n">
         <v>749</v>
       </c>
+      <c r="BN16" t="n">
+        <v>749</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3717,6 +3763,9 @@
       <c r="BM17" t="n">
         <v>1536</v>
       </c>
+      <c r="BN17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3916,6 +3965,9 @@
       <c r="BM18" t="n">
         <v>5.31</v>
       </c>
+      <c r="BN18" t="n">
+        <v>5.23</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4115,6 +4167,9 @@
       <c r="BM19" t="n">
         <v>140.99</v>
       </c>
+      <c r="BN19" t="n">
+        <v>143.19</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4440,6 +4495,11 @@
       <c r="BM20" t="inlineStr">
         <is>
           <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="BN20" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN20"/>
+  <dimension ref="A1:BO20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -742,6 +742,11 @@
           <t>2026-04-30</t>
         </is>
       </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -942,6 +947,9 @@
         <v>4407</v>
       </c>
       <c r="BN2" t="n">
+        <v>4407</v>
+      </c>
+      <c r="BO2" t="n">
         <v>4407</v>
       </c>
     </row>
@@ -1116,6 +1124,9 @@
       <c r="BN3" t="n">
         <v>559</v>
       </c>
+      <c r="BO3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1318,6 +1329,9 @@
       <c r="BN4" t="n">
         <v>1802</v>
       </c>
+      <c r="BO4" t="n">
+        <v>1802</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1518,6 +1532,9 @@
         <v>638</v>
       </c>
       <c r="BN5" t="n">
+        <v>638</v>
+      </c>
+      <c r="BO5" t="n">
         <v>638</v>
       </c>
     </row>
@@ -1692,6 +1709,9 @@
       <c r="BN6" t="n">
         <v>2</v>
       </c>
+      <c r="BO6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1892,6 +1912,9 @@
         <v>2</v>
       </c>
       <c r="BN7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2066,6 +2089,9 @@
       <c r="BN8" t="n">
         <v>19</v>
       </c>
+      <c r="BO8" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2238,6 +2264,9 @@
       <c r="BN9" t="n">
         <v>3</v>
       </c>
+      <c r="BO9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2440,6 +2469,9 @@
       <c r="BN10" t="n">
         <v>1338</v>
       </c>
+      <c r="BO10" t="n">
+        <v>1338</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2642,6 +2674,9 @@
       <c r="BN11" t="n">
         <v>44</v>
       </c>
+      <c r="BO11" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2842,6 +2877,9 @@
         <v>0</v>
       </c>
       <c r="BN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3002,6 +3040,7 @@
       <c r="BL13" t="inlineStr"/>
       <c r="BM13" t="inlineStr"/>
       <c r="BN13" t="inlineStr"/>
+      <c r="BO13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3160,6 +3199,7 @@
       <c r="BL14" t="inlineStr"/>
       <c r="BM14" t="inlineStr"/>
       <c r="BN14" t="inlineStr"/>
+      <c r="BO14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3362,6 +3402,9 @@
       <c r="BN15" t="n">
         <v>65</v>
       </c>
+      <c r="BO15" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3564,6 +3607,9 @@
       <c r="BN16" t="n">
         <v>749</v>
       </c>
+      <c r="BO16" t="n">
+        <v>749</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3766,6 +3812,9 @@
       <c r="BN17" t="n">
         <v>1536</v>
       </c>
+      <c r="BO17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3968,6 +4017,9 @@
       <c r="BN18" t="n">
         <v>5.23</v>
       </c>
+      <c r="BO18" t="n">
+        <v>5.15</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4170,6 +4222,9 @@
       <c r="BN19" t="n">
         <v>143.19</v>
       </c>
+      <c r="BO19" t="n">
+        <v>145.39</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4500,6 +4555,11 @@
       <c r="BN20" t="inlineStr">
         <is>
           <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="BO20" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO20"/>
+  <dimension ref="A1:BP20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -747,6 +747,11 @@
           <t>2026-05-01</t>
         </is>
       </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -950,6 +955,9 @@
         <v>4407</v>
       </c>
       <c r="BO2" t="n">
+        <v>4407</v>
+      </c>
+      <c r="BP2" t="n">
         <v>4407</v>
       </c>
     </row>
@@ -1127,6 +1135,9 @@
       <c r="BO3" t="n">
         <v>559</v>
       </c>
+      <c r="BP3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1332,6 +1343,9 @@
       <c r="BO4" t="n">
         <v>1802</v>
       </c>
+      <c r="BP4" t="n">
+        <v>1802</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1535,6 +1549,9 @@
         <v>638</v>
       </c>
       <c r="BO5" t="n">
+        <v>638</v>
+      </c>
+      <c r="BP5" t="n">
         <v>638</v>
       </c>
     </row>
@@ -1712,6 +1729,9 @@
       <c r="BO6" t="n">
         <v>2</v>
       </c>
+      <c r="BP6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1915,6 +1935,9 @@
         <v>2</v>
       </c>
       <c r="BO7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2092,6 +2115,9 @@
       <c r="BO8" t="n">
         <v>19</v>
       </c>
+      <c r="BP8" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2267,6 +2293,9 @@
       <c r="BO9" t="n">
         <v>3</v>
       </c>
+      <c r="BP9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2472,6 +2501,9 @@
       <c r="BO10" t="n">
         <v>1338</v>
       </c>
+      <c r="BP10" t="n">
+        <v>1338</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2677,6 +2709,9 @@
       <c r="BO11" t="n">
         <v>44</v>
       </c>
+      <c r="BP11" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2880,6 +2915,9 @@
         <v>0</v>
       </c>
       <c r="BO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3041,6 +3079,7 @@
       <c r="BM13" t="inlineStr"/>
       <c r="BN13" t="inlineStr"/>
       <c r="BO13" t="inlineStr"/>
+      <c r="BP13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3200,6 +3239,7 @@
       <c r="BM14" t="inlineStr"/>
       <c r="BN14" t="inlineStr"/>
       <c r="BO14" t="inlineStr"/>
+      <c r="BP14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3405,6 +3445,9 @@
       <c r="BO15" t="n">
         <v>65</v>
       </c>
+      <c r="BP15" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3610,6 +3653,9 @@
       <c r="BO16" t="n">
         <v>749</v>
       </c>
+      <c r="BP16" t="n">
+        <v>749</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3815,6 +3861,9 @@
       <c r="BO17" t="n">
         <v>1536</v>
       </c>
+      <c r="BP17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4020,6 +4069,9 @@
       <c r="BO18" t="n">
         <v>5.15</v>
       </c>
+      <c r="BP18" t="n">
+        <v>5.07</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4225,6 +4277,9 @@
       <c r="BO19" t="n">
         <v>145.39</v>
       </c>
+      <c r="BP19" t="n">
+        <v>147.6</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4560,6 +4615,11 @@
       <c r="BO20" t="inlineStr">
         <is>
           <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="BP20" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP20"/>
+  <dimension ref="A1:BQ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -752,6 +752,11 @@
           <t>2026-05-02</t>
         </is>
       </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -958,6 +963,9 @@
         <v>4407</v>
       </c>
       <c r="BP2" t="n">
+        <v>4407</v>
+      </c>
+      <c r="BQ2" t="n">
         <v>4407</v>
       </c>
     </row>
@@ -1138,6 +1146,9 @@
       <c r="BP3" t="n">
         <v>559</v>
       </c>
+      <c r="BQ3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1346,6 +1357,9 @@
       <c r="BP4" t="n">
         <v>1802</v>
       </c>
+      <c r="BQ4" t="n">
+        <v>1802</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1552,6 +1566,9 @@
         <v>638</v>
       </c>
       <c r="BP5" t="n">
+        <v>638</v>
+      </c>
+      <c r="BQ5" t="n">
         <v>638</v>
       </c>
     </row>
@@ -1732,6 +1749,9 @@
       <c r="BP6" t="n">
         <v>2</v>
       </c>
+      <c r="BQ6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1938,6 +1958,9 @@
         <v>2</v>
       </c>
       <c r="BP7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2118,6 +2141,9 @@
       <c r="BP8" t="n">
         <v>19</v>
       </c>
+      <c r="BQ8" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2296,6 +2322,9 @@
       <c r="BP9" t="n">
         <v>3</v>
       </c>
+      <c r="BQ9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2504,6 +2533,9 @@
       <c r="BP10" t="n">
         <v>1338</v>
       </c>
+      <c r="BQ10" t="n">
+        <v>1338</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2712,6 +2744,9 @@
       <c r="BP11" t="n">
         <v>44</v>
       </c>
+      <c r="BQ11" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2918,6 +2953,9 @@
         <v>0</v>
       </c>
       <c r="BP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3080,6 +3118,7 @@
       <c r="BN13" t="inlineStr"/>
       <c r="BO13" t="inlineStr"/>
       <c r="BP13" t="inlineStr"/>
+      <c r="BQ13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3240,6 +3279,7 @@
       <c r="BN14" t="inlineStr"/>
       <c r="BO14" t="inlineStr"/>
       <c r="BP14" t="inlineStr"/>
+      <c r="BQ14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3448,6 +3488,9 @@
       <c r="BP15" t="n">
         <v>65</v>
       </c>
+      <c r="BQ15" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3656,6 +3699,9 @@
       <c r="BP16" t="n">
         <v>749</v>
       </c>
+      <c r="BQ16" t="n">
+        <v>749</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3864,6 +3910,9 @@
       <c r="BP17" t="n">
         <v>1536</v>
       </c>
+      <c r="BQ17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4072,6 +4121,9 @@
       <c r="BP18" t="n">
         <v>5.07</v>
       </c>
+      <c r="BQ18" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4280,6 +4332,9 @@
       <c r="BP19" t="n">
         <v>147.6</v>
       </c>
+      <c r="BQ19" t="n">
+        <v>149.8</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4620,6 +4675,11 @@
       <c r="BP20" t="inlineStr">
         <is>
           <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="BQ20" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ20"/>
+  <dimension ref="A1:BR20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,6 +757,11 @@
           <t>2026-05-04</t>
         </is>
       </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -966,6 +971,9 @@
         <v>4407</v>
       </c>
       <c r="BQ2" t="n">
+        <v>4407</v>
+      </c>
+      <c r="BR2" t="n">
         <v>4407</v>
       </c>
     </row>
@@ -1149,6 +1157,9 @@
       <c r="BQ3" t="n">
         <v>559</v>
       </c>
+      <c r="BR3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1360,6 +1371,9 @@
       <c r="BQ4" t="n">
         <v>1802</v>
       </c>
+      <c r="BR4" t="n">
+        <v>1802</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1569,6 +1583,9 @@
         <v>638</v>
       </c>
       <c r="BQ5" t="n">
+        <v>638</v>
+      </c>
+      <c r="BR5" t="n">
         <v>638</v>
       </c>
     </row>
@@ -1752,6 +1769,9 @@
       <c r="BQ6" t="n">
         <v>2</v>
       </c>
+      <c r="BR6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1961,6 +1981,9 @@
         <v>2</v>
       </c>
       <c r="BQ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2144,6 +2167,9 @@
       <c r="BQ8" t="n">
         <v>19</v>
       </c>
+      <c r="BR8" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2325,6 +2351,9 @@
       <c r="BQ9" t="n">
         <v>3</v>
       </c>
+      <c r="BR9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2536,6 +2565,9 @@
       <c r="BQ10" t="n">
         <v>1338</v>
       </c>
+      <c r="BR10" t="n">
+        <v>1338</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2747,6 +2779,9 @@
       <c r="BQ11" t="n">
         <v>44</v>
       </c>
+      <c r="BR11" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2956,6 +2991,9 @@
         <v>0</v>
       </c>
       <c r="BQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3119,6 +3157,7 @@
       <c r="BO13" t="inlineStr"/>
       <c r="BP13" t="inlineStr"/>
       <c r="BQ13" t="inlineStr"/>
+      <c r="BR13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3280,6 +3319,7 @@
       <c r="BO14" t="inlineStr"/>
       <c r="BP14" t="inlineStr"/>
       <c r="BQ14" t="inlineStr"/>
+      <c r="BR14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3491,6 +3531,9 @@
       <c r="BQ15" t="n">
         <v>65</v>
       </c>
+      <c r="BR15" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3702,6 +3745,9 @@
       <c r="BQ16" t="n">
         <v>749</v>
       </c>
+      <c r="BR16" t="n">
+        <v>749</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3913,6 +3959,9 @@
       <c r="BQ17" t="n">
         <v>1536</v>
       </c>
+      <c r="BR17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4124,6 +4173,9 @@
       <c r="BQ18" t="n">
         <v>5</v>
       </c>
+      <c r="BR18" t="n">
+        <v>4.93</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4335,6 +4387,9 @@
       <c r="BQ19" t="n">
         <v>149.8</v>
       </c>
+      <c r="BR19" t="n">
+        <v>152</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4680,6 +4735,11 @@
       <c r="BQ20" t="inlineStr">
         <is>
           <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR20"/>
+  <dimension ref="A1:BS20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,6 +762,11 @@
           <t>2026-05-05</t>
         </is>
       </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -975,6 +980,9 @@
       </c>
       <c r="BR2" t="n">
         <v>4407</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>4382</v>
       </c>
     </row>
     <row r="3">
@@ -1160,6 +1168,9 @@
       <c r="BR3" t="n">
         <v>559</v>
       </c>
+      <c r="BS3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1374,6 +1385,9 @@
       <c r="BR4" t="n">
         <v>1802</v>
       </c>
+      <c r="BS4" t="n">
+        <v>1805</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1587,6 +1601,9 @@
       </c>
       <c r="BR5" t="n">
         <v>638</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>513</v>
       </c>
     </row>
     <row r="6">
@@ -1772,6 +1789,9 @@
       <c r="BR6" t="n">
         <v>2</v>
       </c>
+      <c r="BS6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1984,6 +2004,9 @@
         <v>2</v>
       </c>
       <c r="BR7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2170,6 +2193,9 @@
       <c r="BR8" t="n">
         <v>19</v>
       </c>
+      <c r="BS8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2354,6 +2380,9 @@
       <c r="BR9" t="n">
         <v>3</v>
       </c>
+      <c r="BS9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2568,6 +2597,9 @@
       <c r="BR10" t="n">
         <v>1338</v>
       </c>
+      <c r="BS10" t="n">
+        <v>1398</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2782,6 +2814,9 @@
       <c r="BR11" t="n">
         <v>44</v>
       </c>
+      <c r="BS11" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2995,6 +3030,9 @@
       </c>
       <c r="BR12" t="n">
         <v>0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -3158,6 +3196,7 @@
       <c r="BP13" t="inlineStr"/>
       <c r="BQ13" t="inlineStr"/>
       <c r="BR13" t="inlineStr"/>
+      <c r="BS13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3320,6 +3359,7 @@
       <c r="BP14" t="inlineStr"/>
       <c r="BQ14" t="inlineStr"/>
       <c r="BR14" t="inlineStr"/>
+      <c r="BS14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3534,6 +3574,9 @@
       <c r="BR15" t="n">
         <v>65</v>
       </c>
+      <c r="BS15" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3748,6 +3791,9 @@
       <c r="BR16" t="n">
         <v>749</v>
       </c>
+      <c r="BS16" t="n">
+        <v>655</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3962,6 +4008,9 @@
       <c r="BR17" t="n">
         <v>1536</v>
       </c>
+      <c r="BS17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4176,6 +4225,9 @@
       <c r="BR18" t="n">
         <v>4.93</v>
       </c>
+      <c r="BS18" t="n">
+        <v>5.71</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4390,6 +4442,9 @@
       <c r="BR19" t="n">
         <v>152</v>
       </c>
+      <c r="BS19" t="n">
+        <v>114.62</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4740,6 +4795,11 @@
       <c r="BR20" t="inlineStr">
         <is>
           <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="BS20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS20"/>
+  <dimension ref="A1:BT20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -767,6 +767,11 @@
           <t>2026-05-31</t>
         </is>
       </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -983,6 +988,9 @@
       </c>
       <c r="BS2" t="n">
         <v>4382</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>4385</v>
       </c>
     </row>
     <row r="3">
@@ -1171,6 +1179,9 @@
       <c r="BS3" t="n">
         <v>559</v>
       </c>
+      <c r="BT3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1388,6 +1399,9 @@
       <c r="BS4" t="n">
         <v>1805</v>
       </c>
+      <c r="BT4" t="n">
+        <v>1808</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1603,6 +1617,9 @@
         <v>638</v>
       </c>
       <c r="BS5" t="n">
+        <v>513</v>
+      </c>
+      <c r="BT5" t="n">
         <v>513</v>
       </c>
     </row>
@@ -1792,6 +1809,9 @@
       <c r="BS6" t="n">
         <v>2</v>
       </c>
+      <c r="BT6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2007,6 +2027,9 @@
         <v>2</v>
       </c>
       <c r="BS7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2196,6 +2219,9 @@
       <c r="BS8" t="n">
         <v>20</v>
       </c>
+      <c r="BT8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2383,6 +2409,9 @@
       <c r="BS9" t="n">
         <v>3</v>
       </c>
+      <c r="BT9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2600,6 +2629,9 @@
       <c r="BS10" t="n">
         <v>1398</v>
       </c>
+      <c r="BT10" t="n">
+        <v>1398</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2817,6 +2849,9 @@
       <c r="BS11" t="n">
         <v>80</v>
       </c>
+      <c r="BT11" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3033,6 +3068,9 @@
       </c>
       <c r="BS12" t="n">
         <v>60</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3197,6 +3235,7 @@
       <c r="BQ13" t="inlineStr"/>
       <c r="BR13" t="inlineStr"/>
       <c r="BS13" t="inlineStr"/>
+      <c r="BT13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3360,6 +3399,7 @@
       <c r="BQ14" t="inlineStr"/>
       <c r="BR14" t="inlineStr"/>
       <c r="BS14" t="inlineStr"/>
+      <c r="BT14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3577,6 +3617,9 @@
       <c r="BS15" t="n">
         <v>60</v>
       </c>
+      <c r="BT15" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3794,6 +3837,9 @@
       <c r="BS16" t="n">
         <v>655</v>
       </c>
+      <c r="BT16" t="n">
+        <v>655</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4011,6 +4057,9 @@
       <c r="BS17" t="n">
         <v>1536</v>
       </c>
+      <c r="BT17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4228,6 +4277,9 @@
       <c r="BS18" t="n">
         <v>5.71</v>
       </c>
+      <c r="BT18" t="n">
+        <v>5.63</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4445,6 +4497,9 @@
       <c r="BS19" t="n">
         <v>114.62</v>
       </c>
+      <c r="BT19" t="n">
+        <v>116.26</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4800,6 +4855,11 @@
       <c r="BS20" t="inlineStr">
         <is>
           <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="BT20" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BT20"/>
+  <dimension ref="A1:BU20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,6 +772,11 @@
           <t>2026-06-01</t>
         </is>
       </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -990,6 +995,9 @@
         <v>4382</v>
       </c>
       <c r="BT2" t="n">
+        <v>4385</v>
+      </c>
+      <c r="BU2" t="n">
         <v>4385</v>
       </c>
     </row>
@@ -1182,6 +1190,9 @@
       <c r="BT3" t="n">
         <v>559</v>
       </c>
+      <c r="BU3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1402,6 +1413,9 @@
       <c r="BT4" t="n">
         <v>1808</v>
       </c>
+      <c r="BU4" t="n">
+        <v>1808</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1620,6 +1634,9 @@
         <v>513</v>
       </c>
       <c r="BT5" t="n">
+        <v>513</v>
+      </c>
+      <c r="BU5" t="n">
         <v>513</v>
       </c>
     </row>
@@ -1812,6 +1829,9 @@
       <c r="BT6" t="n">
         <v>2</v>
       </c>
+      <c r="BU6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2030,6 +2050,9 @@
         <v>2</v>
       </c>
       <c r="BT7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2222,6 +2245,9 @@
       <c r="BT8" t="n">
         <v>20</v>
       </c>
+      <c r="BU8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2412,6 +2438,9 @@
       <c r="BT9" t="n">
         <v>3</v>
       </c>
+      <c r="BU9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2632,6 +2661,9 @@
       <c r="BT10" t="n">
         <v>1398</v>
       </c>
+      <c r="BU10" t="n">
+        <v>1398</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2852,6 +2884,9 @@
       <c r="BT11" t="n">
         <v>80</v>
       </c>
+      <c r="BU11" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3070,6 +3105,9 @@
         <v>60</v>
       </c>
       <c r="BT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3236,6 +3274,7 @@
       <c r="BR13" t="inlineStr"/>
       <c r="BS13" t="inlineStr"/>
       <c r="BT13" t="inlineStr"/>
+      <c r="BU13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3400,6 +3439,7 @@
       <c r="BR14" t="inlineStr"/>
       <c r="BS14" t="inlineStr"/>
       <c r="BT14" t="inlineStr"/>
+      <c r="BU14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3620,6 +3660,9 @@
       <c r="BT15" t="n">
         <v>60</v>
       </c>
+      <c r="BU15" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3840,6 +3883,9 @@
       <c r="BT16" t="n">
         <v>655</v>
       </c>
+      <c r="BU16" t="n">
+        <v>655</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4060,6 +4106,9 @@
       <c r="BT17" t="n">
         <v>1536</v>
       </c>
+      <c r="BU17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4280,6 +4329,9 @@
       <c r="BT18" t="n">
         <v>5.63</v>
       </c>
+      <c r="BU18" t="n">
+        <v>5.56</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4500,6 +4552,9 @@
       <c r="BT19" t="n">
         <v>116.26</v>
       </c>
+      <c r="BU19" t="n">
+        <v>117.9</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4860,6 +4915,11 @@
       <c r="BT20" t="inlineStr">
         <is>
           <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="BU20" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU20"/>
+  <dimension ref="A1:BV20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -777,6 +777,11 @@
           <t>2026-06-02</t>
         </is>
       </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -998,6 +1003,9 @@
         <v>4385</v>
       </c>
       <c r="BU2" t="n">
+        <v>4385</v>
+      </c>
+      <c r="BV2" t="n">
         <v>4385</v>
       </c>
     </row>
@@ -1193,6 +1201,9 @@
       <c r="BU3" t="n">
         <v>559</v>
       </c>
+      <c r="BV3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1416,6 +1427,9 @@
       <c r="BU4" t="n">
         <v>1808</v>
       </c>
+      <c r="BV4" t="n">
+        <v>1808</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1637,6 +1651,9 @@
         <v>513</v>
       </c>
       <c r="BU5" t="n">
+        <v>513</v>
+      </c>
+      <c r="BV5" t="n">
         <v>513</v>
       </c>
     </row>
@@ -1832,6 +1849,9 @@
       <c r="BU6" t="n">
         <v>2</v>
       </c>
+      <c r="BV6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2053,6 +2073,9 @@
         <v>2</v>
       </c>
       <c r="BU7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BV7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2248,6 +2271,9 @@
       <c r="BU8" t="n">
         <v>20</v>
       </c>
+      <c r="BV8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2441,6 +2467,9 @@
       <c r="BU9" t="n">
         <v>3</v>
       </c>
+      <c r="BV9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2664,6 +2693,9 @@
       <c r="BU10" t="n">
         <v>1398</v>
       </c>
+      <c r="BV10" t="n">
+        <v>1398</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2887,6 +2919,9 @@
       <c r="BU11" t="n">
         <v>80</v>
       </c>
+      <c r="BV11" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3108,6 +3143,9 @@
         <v>0</v>
       </c>
       <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3275,6 +3313,7 @@
       <c r="BS13" t="inlineStr"/>
       <c r="BT13" t="inlineStr"/>
       <c r="BU13" t="inlineStr"/>
+      <c r="BV13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3440,6 +3479,7 @@
       <c r="BS14" t="inlineStr"/>
       <c r="BT14" t="inlineStr"/>
       <c r="BU14" t="inlineStr"/>
+      <c r="BV14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3663,6 +3703,9 @@
       <c r="BU15" t="n">
         <v>60</v>
       </c>
+      <c r="BV15" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3886,6 +3929,9 @@
       <c r="BU16" t="n">
         <v>655</v>
       </c>
+      <c r="BV16" t="n">
+        <v>655</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4109,6 +4155,9 @@
       <c r="BU17" t="n">
         <v>1536</v>
       </c>
+      <c r="BV17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4332,6 +4381,9 @@
       <c r="BU18" t="n">
         <v>5.56</v>
       </c>
+      <c r="BV18" t="n">
+        <v>5.48</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4555,6 +4607,9 @@
       <c r="BU19" t="n">
         <v>117.9</v>
       </c>
+      <c r="BV19" t="n">
+        <v>119.54</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4920,6 +4975,11 @@
       <c r="BU20" t="inlineStr">
         <is>
           <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="BV20" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV20"/>
+  <dimension ref="A1:BW20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,6 +782,11 @@
           <t>2026-06-03</t>
         </is>
       </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1007,6 +1012,9 @@
       </c>
       <c r="BV2" t="n">
         <v>4385</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>4399</v>
       </c>
     </row>
     <row r="3">
@@ -1204,6 +1212,9 @@
       <c r="BV3" t="n">
         <v>559</v>
       </c>
+      <c r="BW3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1430,6 +1441,9 @@
       <c r="BV4" t="n">
         <v>1808</v>
       </c>
+      <c r="BW4" t="n">
+        <v>1822</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1655,6 +1669,9 @@
       </c>
       <c r="BV5" t="n">
         <v>513</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>458</v>
       </c>
     </row>
     <row r="6">
@@ -1852,6 +1869,9 @@
       <c r="BV6" t="n">
         <v>2</v>
       </c>
+      <c r="BW6" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2076,6 +2096,9 @@
         <v>2</v>
       </c>
       <c r="BV7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BW7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2274,6 +2297,9 @@
       <c r="BV8" t="n">
         <v>20</v>
       </c>
+      <c r="BW8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2470,6 +2496,9 @@
       <c r="BV9" t="n">
         <v>3</v>
       </c>
+      <c r="BW9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2696,6 +2725,9 @@
       <c r="BV10" t="n">
         <v>1398</v>
       </c>
+      <c r="BW10" t="n">
+        <v>1447</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2922,6 +2954,9 @@
       <c r="BV11" t="n">
         <v>80</v>
       </c>
+      <c r="BW11" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3147,6 +3182,9 @@
       </c>
       <c r="BV12" t="n">
         <v>0</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -3314,6 +3352,7 @@
       <c r="BT13" t="inlineStr"/>
       <c r="BU13" t="inlineStr"/>
       <c r="BV13" t="inlineStr"/>
+      <c r="BW13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3480,6 +3519,7 @@
       <c r="BT14" t="inlineStr"/>
       <c r="BU14" t="inlineStr"/>
       <c r="BV14" t="inlineStr"/>
+      <c r="BW14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3706,6 +3746,9 @@
       <c r="BV15" t="n">
         <v>60</v>
       </c>
+      <c r="BW15" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3932,6 +3975,9 @@
       <c r="BV16" t="n">
         <v>655</v>
       </c>
+      <c r="BW16" t="n">
+        <v>604</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4158,6 +4204,9 @@
       <c r="BV17" t="n">
         <v>1536</v>
       </c>
+      <c r="BW17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4384,6 +4433,9 @@
       <c r="BV18" t="n">
         <v>5.48</v>
       </c>
+      <c r="BW18" t="n">
+        <v>6.07</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4610,6 +4662,9 @@
       <c r="BV19" t="n">
         <v>119.54</v>
       </c>
+      <c r="BW19" t="n">
+        <v>99.55</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4980,6 +5035,11 @@
       <c r="BV20" t="inlineStr">
         <is>
           <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="BW20" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW20"/>
+  <dimension ref="A1:BX20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,6 +787,11 @@
           <t>2026-06-21</t>
         </is>
       </c>
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1015,6 +1020,9 @@
       </c>
       <c r="BW2" t="n">
         <v>4399</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>4404</v>
       </c>
     </row>
     <row r="3">
@@ -1215,6 +1223,9 @@
       <c r="BW3" t="n">
         <v>559</v>
       </c>
+      <c r="BX3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1444,6 +1455,9 @@
       <c r="BW4" t="n">
         <v>1822</v>
       </c>
+      <c r="BX4" t="n">
+        <v>1827</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1672,6 +1686,9 @@
       </c>
       <c r="BW5" t="n">
         <v>458</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>439</v>
       </c>
     </row>
     <row r="6">
@@ -1872,6 +1889,9 @@
       <c r="BW6" t="n">
         <v>4</v>
       </c>
+      <c r="BX6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2099,6 +2119,9 @@
         <v>2</v>
       </c>
       <c r="BW7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BX7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2300,6 +2323,9 @@
       <c r="BW8" t="n">
         <v>20</v>
       </c>
+      <c r="BX8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2499,6 +2525,9 @@
       <c r="BW9" t="n">
         <v>3</v>
       </c>
+      <c r="BX9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2728,6 +2757,9 @@
       <c r="BW10" t="n">
         <v>1447</v>
       </c>
+      <c r="BX10" t="n">
+        <v>1519</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2957,6 +2989,9 @@
       <c r="BW11" t="n">
         <v>84</v>
       </c>
+      <c r="BX11" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3185,6 +3220,9 @@
       </c>
       <c r="BW12" t="n">
         <v>49</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -3353,6 +3391,7 @@
       <c r="BU13" t="inlineStr"/>
       <c r="BV13" t="inlineStr"/>
       <c r="BW13" t="inlineStr"/>
+      <c r="BX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3520,6 +3559,7 @@
       <c r="BU14" t="inlineStr"/>
       <c r="BV14" t="inlineStr"/>
       <c r="BW14" t="inlineStr"/>
+      <c r="BX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3749,6 +3789,9 @@
       <c r="BW15" t="n">
         <v>60</v>
       </c>
+      <c r="BX15" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3978,6 +4021,9 @@
       <c r="BW16" t="n">
         <v>604</v>
       </c>
+      <c r="BX16" t="n">
+        <v>531</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4207,6 +4253,9 @@
       <c r="BW17" t="n">
         <v>1536</v>
       </c>
+      <c r="BX17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4436,6 +4485,9 @@
       <c r="BW18" t="n">
         <v>6.07</v>
       </c>
+      <c r="BX18" t="n">
+        <v>6.95</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4665,6 +4717,9 @@
       <c r="BW19" t="n">
         <v>99.55</v>
       </c>
+      <c r="BX19" t="n">
+        <v>76.44</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5040,6 +5095,11 @@
       <c r="BW20" t="inlineStr">
         <is>
           <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="BX20" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX20"/>
+  <dimension ref="A1:BY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,6 +792,11 @@
           <t>2026-06-28</t>
         </is>
       </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1022,6 +1027,9 @@
         <v>4399</v>
       </c>
       <c r="BX2" t="n">
+        <v>4404</v>
+      </c>
+      <c r="BY2" t="n">
         <v>4404</v>
       </c>
     </row>
@@ -1226,6 +1234,9 @@
       <c r="BX3" t="n">
         <v>559</v>
       </c>
+      <c r="BY3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1458,6 +1469,9 @@
       <c r="BX4" t="n">
         <v>1827</v>
       </c>
+      <c r="BY4" t="n">
+        <v>1827</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1688,6 +1702,9 @@
         <v>458</v>
       </c>
       <c r="BX5" t="n">
+        <v>439</v>
+      </c>
+      <c r="BY5" t="n">
         <v>439</v>
       </c>
     </row>
@@ -1892,6 +1909,9 @@
       <c r="BX6" t="n">
         <v>5</v>
       </c>
+      <c r="BY6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2122,6 +2142,9 @@
         <v>2</v>
       </c>
       <c r="BX7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BY7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2326,6 +2349,9 @@
       <c r="BX8" t="n">
         <v>20</v>
       </c>
+      <c r="BY8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2528,6 +2554,9 @@
       <c r="BX9" t="n">
         <v>3</v>
       </c>
+      <c r="BY9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2760,6 +2789,9 @@
       <c r="BX10" t="n">
         <v>1519</v>
       </c>
+      <c r="BY10" t="n">
+        <v>1519</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2992,6 +3024,9 @@
       <c r="BX11" t="n">
         <v>30</v>
       </c>
+      <c r="BY11" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3223,6 +3258,9 @@
       </c>
       <c r="BX12" t="n">
         <v>72</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3392,6 +3430,7 @@
       <c r="BV13" t="inlineStr"/>
       <c r="BW13" t="inlineStr"/>
       <c r="BX13" t="inlineStr"/>
+      <c r="BY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3560,6 +3599,7 @@
       <c r="BV14" t="inlineStr"/>
       <c r="BW14" t="inlineStr"/>
       <c r="BX14" t="inlineStr"/>
+      <c r="BY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3792,6 +3832,9 @@
       <c r="BX15" t="n">
         <v>60</v>
       </c>
+      <c r="BY15" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4024,6 +4067,9 @@
       <c r="BX16" t="n">
         <v>531</v>
       </c>
+      <c r="BY16" t="n">
+        <v>531</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4256,6 +4302,9 @@
       <c r="BX17" t="n">
         <v>1536</v>
       </c>
+      <c r="BY17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4488,6 +4537,9 @@
       <c r="BX18" t="n">
         <v>6.95</v>
       </c>
+      <c r="BY18" t="n">
+        <v>6.86</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4720,6 +4772,9 @@
       <c r="BX19" t="n">
         <v>76.44</v>
       </c>
+      <c r="BY19" t="n">
+        <v>77.45999999999999</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5100,6 +5155,11 @@
       <c r="BX20" t="inlineStr">
         <is>
           <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="BY20" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -1705,7 +1705,7 @@
         <v>439</v>
       </c>
       <c r="BY5" t="n">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="6">
@@ -1910,7 +1910,7 @@
         <v>5</v>
       </c>
       <c r="BY6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -2790,7 +2790,7 @@
         <v>1519</v>
       </c>
       <c r="BY10" t="n">
-        <v>1519</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="11">
@@ -3025,7 +3025,7 @@
         <v>30</v>
       </c>
       <c r="BY11" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12">
@@ -3260,7 +3260,7 @@
         <v>72</v>
       </c>
       <c r="BY12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -4068,7 +4068,7 @@
         <v>531</v>
       </c>
       <c r="BY16" t="n">
-        <v>531</v>
+        <v>522</v>
       </c>
     </row>
     <row r="17">
@@ -4538,7 +4538,7 @@
         <v>6.95</v>
       </c>
       <c r="BY18" t="n">
-        <v>6.86</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="19">
@@ -4773,7 +4773,7 @@
         <v>76.44</v>
       </c>
       <c r="BY19" t="n">
-        <v>77.45999999999999</v>
+        <v>74.70999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY20"/>
+  <dimension ref="A1:BZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,6 +797,11 @@
           <t>2026-06-29</t>
         </is>
       </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1030,6 +1035,9 @@
         <v>4404</v>
       </c>
       <c r="BY2" t="n">
+        <v>4404</v>
+      </c>
+      <c r="BZ2" t="n">
         <v>4404</v>
       </c>
     </row>
@@ -1237,6 +1245,9 @@
       <c r="BY3" t="n">
         <v>559</v>
       </c>
+      <c r="BZ3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1472,6 +1483,9 @@
       <c r="BY4" t="n">
         <v>1827</v>
       </c>
+      <c r="BZ4" t="n">
+        <v>1827</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1705,6 +1719,9 @@
         <v>439</v>
       </c>
       <c r="BY5" t="n">
+        <v>436</v>
+      </c>
+      <c r="BZ5" t="n">
         <v>436</v>
       </c>
     </row>
@@ -1912,6 +1929,9 @@
       <c r="BY6" t="n">
         <v>4</v>
       </c>
+      <c r="BZ6" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2145,6 +2165,9 @@
         <v>2</v>
       </c>
       <c r="BY7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BZ7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2352,6 +2375,9 @@
       <c r="BY8" t="n">
         <v>20</v>
       </c>
+      <c r="BZ8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2557,6 +2583,9 @@
       <c r="BY9" t="n">
         <v>3</v>
       </c>
+      <c r="BZ9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2792,6 +2821,9 @@
       <c r="BY10" t="n">
         <v>1529</v>
       </c>
+      <c r="BZ10" t="n">
+        <v>1529</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3027,6 +3059,9 @@
       <c r="BY11" t="n">
         <v>24</v>
       </c>
+      <c r="BZ11" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3261,6 +3296,9 @@
       </c>
       <c r="BY12" t="n">
         <v>10</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3431,6 +3469,7 @@
       <c r="BW13" t="inlineStr"/>
       <c r="BX13" t="inlineStr"/>
       <c r="BY13" t="inlineStr"/>
+      <c r="BZ13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3600,6 +3639,7 @@
       <c r="BW14" t="inlineStr"/>
       <c r="BX14" t="inlineStr"/>
       <c r="BY14" t="inlineStr"/>
+      <c r="BZ14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3835,6 +3875,9 @@
       <c r="BY15" t="n">
         <v>60</v>
       </c>
+      <c r="BZ15" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4070,6 +4113,9 @@
       <c r="BY16" t="n">
         <v>522</v>
       </c>
+      <c r="BZ16" t="n">
+        <v>522</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4305,6 +4351,9 @@
       <c r="BY17" t="n">
         <v>1536</v>
       </c>
+      <c r="BZ17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4540,6 +4589,9 @@
       <c r="BY18" t="n">
         <v>6.99</v>
       </c>
+      <c r="BZ18" t="n">
+        <v>6.9</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4775,6 +4827,9 @@
       <c r="BY19" t="n">
         <v>74.70999999999999</v>
       </c>
+      <c r="BZ19" t="n">
+        <v>75.69</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5160,6 +5215,11 @@
       <c r="BY20" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="BZ20" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -1722,7 +1722,7 @@
         <v>436</v>
       </c>
       <c r="BZ5" t="n">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="6">
@@ -1930,7 +1930,7 @@
         <v>4</v>
       </c>
       <c r="BZ6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -2822,7 +2822,7 @@
         <v>1529</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1529</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="11">
@@ -3060,7 +3060,7 @@
         <v>24</v>
       </c>
       <c r="BZ11" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
@@ -3298,7 +3298,7 @@
         <v>10</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -4114,7 +4114,7 @@
         <v>522</v>
       </c>
       <c r="BZ16" t="n">
-        <v>522</v>
+        <v>513</v>
       </c>
     </row>
     <row r="17">
@@ -4590,7 +4590,7 @@
         <v>6.99</v>
       </c>
       <c r="BZ18" t="n">
-        <v>6.9</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="19">
@@ -4828,7 +4828,7 @@
         <v>74.70999999999999</v>
       </c>
       <c r="BZ19" t="n">
-        <v>75.69</v>
+        <v>72.75</v>
       </c>
     </row>
     <row r="20">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ20"/>
+  <dimension ref="A1:CA20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -802,6 +802,11 @@
           <t>2026-06-30</t>
         </is>
       </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1039,6 +1044,9 @@
       </c>
       <c r="BZ2" t="n">
         <v>4404</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>4405</v>
       </c>
     </row>
     <row r="3">
@@ -1248,6 +1256,9 @@
       <c r="BZ3" t="n">
         <v>559</v>
       </c>
+      <c r="CA3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1486,6 +1497,9 @@
       <c r="BZ4" t="n">
         <v>1827</v>
       </c>
+      <c r="CA4" t="n">
+        <v>1828</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1723,6 +1737,9 @@
       </c>
       <c r="BZ5" t="n">
         <v>434</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>429</v>
       </c>
     </row>
     <row r="6">
@@ -1932,6 +1949,7 @@
       <c r="BZ6" t="n">
         <v>1</v>
       </c>
+      <c r="CA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2168,6 +2186,9 @@
         <v>2</v>
       </c>
       <c r="BZ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="CA7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2378,6 +2399,9 @@
       <c r="BZ8" t="n">
         <v>20</v>
       </c>
+      <c r="CA8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2586,6 +2610,9 @@
       <c r="BZ9" t="n">
         <v>3</v>
       </c>
+      <c r="CA9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2824,6 +2851,9 @@
       <c r="BZ10" t="n">
         <v>1541</v>
       </c>
+      <c r="CA10" t="n">
+        <v>1556</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3062,6 +3092,9 @@
       <c r="BZ11" t="n">
         <v>17</v>
       </c>
+      <c r="CA11" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3299,6 +3332,9 @@
       </c>
       <c r="BZ12" t="n">
         <v>12</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -3470,6 +3506,7 @@
       <c r="BX13" t="inlineStr"/>
       <c r="BY13" t="inlineStr"/>
       <c r="BZ13" t="inlineStr"/>
+      <c r="CA13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3640,6 +3677,7 @@
       <c r="BX14" t="inlineStr"/>
       <c r="BY14" t="inlineStr"/>
       <c r="BZ14" t="inlineStr"/>
+      <c r="CA14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3878,6 +3916,9 @@
       <c r="BZ15" t="n">
         <v>60</v>
       </c>
+      <c r="CA15" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4116,6 +4157,9 @@
       <c r="BZ16" t="n">
         <v>513</v>
       </c>
+      <c r="CA16" t="n">
+        <v>499</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4354,6 +4398,9 @@
       <c r="BZ17" t="n">
         <v>1536</v>
       </c>
+      <c r="CA17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4592,6 +4639,9 @@
       <c r="BZ18" t="n">
         <v>7.05</v>
       </c>
+      <c r="CA18" t="n">
+        <v>7.15</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4830,6 +4880,9 @@
       <c r="BZ19" t="n">
         <v>72.75</v>
       </c>
+      <c r="CA19" t="n">
+        <v>69.75</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5220,6 +5273,11 @@
       <c r="BZ20" t="inlineStr">
         <is>
           <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="CA20" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA20"/>
+  <dimension ref="A1:CB20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -807,6 +807,11 @@
           <t>2026-07-01</t>
         </is>
       </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1046,6 +1051,9 @@
         <v>4404</v>
       </c>
       <c r="CA2" t="n">
+        <v>4405</v>
+      </c>
+      <c r="CB2" t="n">
         <v>4405</v>
       </c>
     </row>
@@ -1259,6 +1267,9 @@
       <c r="CA3" t="n">
         <v>559</v>
       </c>
+      <c r="CB3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1500,6 +1511,9 @@
       <c r="CA4" t="n">
         <v>1828</v>
       </c>
+      <c r="CB4" t="n">
+        <v>1828</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1739,6 +1753,9 @@
         <v>434</v>
       </c>
       <c r="CA5" t="n">
+        <v>429</v>
+      </c>
+      <c r="CB5" t="n">
         <v>429</v>
       </c>
     </row>
@@ -1950,6 +1967,7 @@
         <v>1</v>
       </c>
       <c r="CA6" t="inlineStr"/>
+      <c r="CB6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2189,6 +2207,9 @@
         <v>2</v>
       </c>
       <c r="CA7" t="n">
+        <v>2</v>
+      </c>
+      <c r="CB7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2402,6 +2423,9 @@
       <c r="CA8" t="n">
         <v>20</v>
       </c>
+      <c r="CB8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2613,6 +2637,9 @@
       <c r="CA9" t="n">
         <v>3</v>
       </c>
+      <c r="CB9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2854,6 +2881,9 @@
       <c r="CA10" t="n">
         <v>1556</v>
       </c>
+      <c r="CB10" t="n">
+        <v>1556</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3095,6 +3125,9 @@
       <c r="CA11" t="n">
         <v>8</v>
       </c>
+      <c r="CB11" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3335,6 +3368,9 @@
       </c>
       <c r="CA12" t="n">
         <v>15</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3507,6 +3543,7 @@
       <c r="BY13" t="inlineStr"/>
       <c r="BZ13" t="inlineStr"/>
       <c r="CA13" t="inlineStr"/>
+      <c r="CB13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3678,6 +3715,7 @@
       <c r="BY14" t="inlineStr"/>
       <c r="BZ14" t="inlineStr"/>
       <c r="CA14" t="inlineStr"/>
+      <c r="CB14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3919,6 +3957,9 @@
       <c r="CA15" t="n">
         <v>60</v>
       </c>
+      <c r="CB15" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4160,6 +4201,9 @@
       <c r="CA16" t="n">
         <v>499</v>
       </c>
+      <c r="CB16" t="n">
+        <v>499</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4401,6 +4445,9 @@
       <c r="CA17" t="n">
         <v>1536</v>
       </c>
+      <c r="CB17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4642,6 +4689,9 @@
       <c r="CA18" t="n">
         <v>7.15</v>
       </c>
+      <c r="CB18" t="n">
+        <v>7.06</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4883,6 +4933,9 @@
       <c r="CA19" t="n">
         <v>69.75</v>
       </c>
+      <c r="CB19" t="n">
+        <v>70.65000000000001</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5278,6 +5331,11 @@
       <c r="CA20" t="inlineStr">
         <is>
           <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB20"/>
+  <dimension ref="A1:CC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,6 +812,11 @@
           <t>2026-07-02</t>
         </is>
       </c>
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1054,6 +1059,9 @@
         <v>4405</v>
       </c>
       <c r="CB2" t="n">
+        <v>4405</v>
+      </c>
+      <c r="CC2" t="n">
         <v>4405</v>
       </c>
     </row>
@@ -1270,6 +1278,9 @@
       <c r="CB3" t="n">
         <v>559</v>
       </c>
+      <c r="CC3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1514,6 +1525,9 @@
       <c r="CB4" t="n">
         <v>1828</v>
       </c>
+      <c r="CC4" t="n">
+        <v>1828</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1756,6 +1770,9 @@
         <v>429</v>
       </c>
       <c r="CB5" t="n">
+        <v>429</v>
+      </c>
+      <c r="CC5" t="n">
         <v>429</v>
       </c>
     </row>
@@ -1968,6 +1985,7 @@
       </c>
       <c r="CA6" t="inlineStr"/>
       <c r="CB6" t="inlineStr"/>
+      <c r="CC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2210,6 +2228,9 @@
         <v>2</v>
       </c>
       <c r="CB7" t="n">
+        <v>2</v>
+      </c>
+      <c r="CC7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2426,6 +2447,9 @@
       <c r="CB8" t="n">
         <v>20</v>
       </c>
+      <c r="CC8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2640,6 +2664,9 @@
       <c r="CB9" t="n">
         <v>3</v>
       </c>
+      <c r="CC9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2884,6 +2911,9 @@
       <c r="CB10" t="n">
         <v>1556</v>
       </c>
+      <c r="CC10" t="n">
+        <v>1556</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3128,6 +3158,9 @@
       <c r="CB11" t="n">
         <v>8</v>
       </c>
+      <c r="CC11" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3370,6 +3403,9 @@
         <v>15</v>
       </c>
       <c r="CB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3544,6 +3580,7 @@
       <c r="BZ13" t="inlineStr"/>
       <c r="CA13" t="inlineStr"/>
       <c r="CB13" t="inlineStr"/>
+      <c r="CC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3716,6 +3753,7 @@
       <c r="BZ14" t="inlineStr"/>
       <c r="CA14" t="inlineStr"/>
       <c r="CB14" t="inlineStr"/>
+      <c r="CC14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3960,6 +3998,9 @@
       <c r="CB15" t="n">
         <v>60</v>
       </c>
+      <c r="CC15" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4204,6 +4245,9 @@
       <c r="CB16" t="n">
         <v>499</v>
       </c>
+      <c r="CC16" t="n">
+        <v>499</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4448,6 +4492,9 @@
       <c r="CB17" t="n">
         <v>1536</v>
       </c>
+      <c r="CC17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4692,6 +4739,9 @@
       <c r="CB18" t="n">
         <v>7.06</v>
       </c>
+      <c r="CC18" t="n">
+        <v>6.97</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4936,6 +4986,9 @@
       <c r="CB19" t="n">
         <v>70.65000000000001</v>
       </c>
+      <c r="CC19" t="n">
+        <v>71.54000000000001</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5336,6 +5389,11 @@
       <c r="CB20" t="inlineStr">
         <is>
           <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="CC20" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CC20"/>
+  <dimension ref="A1:CD20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -817,6 +817,11 @@
           <t>2026-07-03</t>
         </is>
       </c>
+      <c r="CD1" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1062,6 +1067,9 @@
         <v>4405</v>
       </c>
       <c r="CC2" t="n">
+        <v>4405</v>
+      </c>
+      <c r="CD2" t="n">
         <v>4405</v>
       </c>
     </row>
@@ -1281,6 +1289,9 @@
       <c r="CC3" t="n">
         <v>559</v>
       </c>
+      <c r="CD3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1528,6 +1539,9 @@
       <c r="CC4" t="n">
         <v>1828</v>
       </c>
+      <c r="CD4" t="n">
+        <v>1828</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1773,6 +1787,9 @@
         <v>429</v>
       </c>
       <c r="CC5" t="n">
+        <v>429</v>
+      </c>
+      <c r="CD5" t="n">
         <v>429</v>
       </c>
     </row>
@@ -1986,6 +2003,7 @@
       <c r="CA6" t="inlineStr"/>
       <c r="CB6" t="inlineStr"/>
       <c r="CC6" t="inlineStr"/>
+      <c r="CD6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2231,6 +2249,9 @@
         <v>2</v>
       </c>
       <c r="CC7" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2450,6 +2471,9 @@
       <c r="CC8" t="n">
         <v>20</v>
       </c>
+      <c r="CD8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2667,6 +2691,9 @@
       <c r="CC9" t="n">
         <v>3</v>
       </c>
+      <c r="CD9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2914,6 +2941,9 @@
       <c r="CC10" t="n">
         <v>1556</v>
       </c>
+      <c r="CD10" t="n">
+        <v>1556</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3161,6 +3191,9 @@
       <c r="CC11" t="n">
         <v>8</v>
       </c>
+      <c r="CD11" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3406,6 +3439,9 @@
         <v>0</v>
       </c>
       <c r="CC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3581,6 +3617,7 @@
       <c r="CA13" t="inlineStr"/>
       <c r="CB13" t="inlineStr"/>
       <c r="CC13" t="inlineStr"/>
+      <c r="CD13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3754,6 +3791,7 @@
       <c r="CA14" t="inlineStr"/>
       <c r="CB14" t="inlineStr"/>
       <c r="CC14" t="inlineStr"/>
+      <c r="CD14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4001,6 +4039,9 @@
       <c r="CC15" t="n">
         <v>60</v>
       </c>
+      <c r="CD15" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4248,6 +4289,9 @@
       <c r="CC16" t="n">
         <v>499</v>
       </c>
+      <c r="CD16" t="n">
+        <v>499</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4495,6 +4539,9 @@
       <c r="CC17" t="n">
         <v>1536</v>
       </c>
+      <c r="CD17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4742,6 +4789,9 @@
       <c r="CC18" t="n">
         <v>6.97</v>
       </c>
+      <c r="CD18" t="n">
+        <v>6.89</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4989,6 +5039,9 @@
       <c r="CC19" t="n">
         <v>71.54000000000001</v>
       </c>
+      <c r="CD19" t="n">
+        <v>72.44</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5394,6 +5447,11 @@
       <c r="CC20" t="inlineStr">
         <is>
           <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="CD20" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -1790,7 +1790,7 @@
         <v>429</v>
       </c>
       <c r="CD5" t="n">
-        <v>429</v>
+        <v>411</v>
       </c>
     </row>
     <row r="6">
@@ -2942,7 +2942,7 @@
         <v>1556</v>
       </c>
       <c r="CD10" t="n">
-        <v>1556</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="11">
@@ -3192,7 +3192,7 @@
         <v>8</v>
       </c>
       <c r="CD11" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
@@ -3442,7 +3442,7 @@
         <v>0</v>
       </c>
       <c r="CD12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -4290,7 +4290,7 @@
         <v>499</v>
       </c>
       <c r="CD16" t="n">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="17">
@@ -4790,7 +4790,7 @@
         <v>6.97</v>
       </c>
       <c r="CD18" t="n">
-        <v>6.89</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="19">
@@ -5040,7 +5040,7 @@
         <v>71.54000000000001</v>
       </c>
       <c r="CD19" t="n">
-        <v>72.44</v>
+        <v>72.16</v>
       </c>
     </row>
     <row r="20">

--- a/docs/historico_giuriolo.xlsx
+++ b/docs/historico_giuriolo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CD20"/>
+  <dimension ref="A1:CE20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -822,6 +822,11 @@
           <t>2026-07-04</t>
         </is>
       </c>
+      <c r="CE1" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1070,6 +1075,9 @@
         <v>4405</v>
       </c>
       <c r="CD2" t="n">
+        <v>4405</v>
+      </c>
+      <c r="CE2" t="n">
         <v>4405</v>
       </c>
     </row>
@@ -1292,6 +1300,9 @@
       <c r="CD3" t="n">
         <v>559</v>
       </c>
+      <c r="CE3" t="n">
+        <v>559</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1542,6 +1553,9 @@
       <c r="CD4" t="n">
         <v>1828</v>
       </c>
+      <c r="CE4" t="n">
+        <v>1828</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1791,6 +1805,9 @@
       </c>
       <c r="CD5" t="n">
         <v>411</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>409</v>
       </c>
     </row>
     <row r="6">
@@ -2004,6 +2021,7 @@
       <c r="CB6" t="inlineStr"/>
       <c r="CC6" t="inlineStr"/>
       <c r="CD6" t="inlineStr"/>
+      <c r="CE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2252,6 +2270,9 @@
         <v>2</v>
       </c>
       <c r="CD7" t="n">
+        <v>2</v>
+      </c>
+      <c r="CE7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2474,6 +2495,9 @@
       <c r="CD8" t="n">
         <v>20</v>
       </c>
+      <c r="CE8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2694,6 +2718,9 @@
       <c r="CD9" t="n">
         <v>3</v>
       </c>
+      <c r="CE9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2944,6 +2971,9 @@
       <c r="CD10" t="n">
         <v>1557</v>
       </c>
+      <c r="CE10" t="n">
+        <v>1557</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3194,6 +3224,9 @@
       <c r="CD11" t="n">
         <v>25</v>
       </c>
+      <c r="CE11" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3443,6 +3476,9 @@
       </c>
       <c r="CD12" t="n">
         <v>1</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3618,6 +3654,7 @@
       <c r="CB13" t="inlineStr"/>
       <c r="CC13" t="inlineStr"/>
       <c r="CD13" t="inlineStr"/>
+      <c r="CE13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3792,6 +3829,7 @@
       <c r="CB14" t="inlineStr"/>
       <c r="CC14" t="inlineStr"/>
       <c r="CD14" t="inlineStr"/>
+      <c r="CE14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4042,6 +4080,9 @@
       <c r="CD15" t="n">
         <v>60</v>
       </c>
+      <c r="CE15" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4292,6 +4333,9 @@
       <c r="CD16" t="n">
         <v>498</v>
       </c>
+      <c r="CE16" t="n">
+        <v>498</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4542,6 +4586,9 @@
       <c r="CD17" t="n">
         <v>1536</v>
       </c>
+      <c r="CE17" t="n">
+        <v>1536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4792,6 +4839,9 @@
       <c r="CD18" t="n">
         <v>6.9</v>
       </c>
+      <c r="CE18" t="n">
+        <v>6.82</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5042,6 +5092,9 @@
       <c r="CD19" t="n">
         <v>72.16</v>
       </c>
+      <c r="CE19" t="n">
+        <v>73.05</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5452,6 +5505,11 @@
       <c r="CD20" t="inlineStr">
         <is>
           <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
